--- a/docs/forms/Форма-40.xlsx
+++ b/docs/forms/Форма-40.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266C5F88-E25F-4A3B-BE47-FB71D7F770A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1129EF-C0D3-4E63-ACF7-6AA283234C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="WVTMOiQwR85XTisTO4DKrfISZxNQ0BFpECcCCS000Uu+GkxcfHR6areMxt2yyc5aaThY5MfMfYqeI/nYPU05nQ==" workbookSaltValue="ribmnAY1Ux88SofCBxYDaA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -15,16 +15,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Форма № 40'!$A$1:$AI$60</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="179">
   <si>
     <t>1.</t>
   </si>
@@ -666,9 +661,6 @@
   </si>
   <si>
     <t>2025</t>
-  </si>
-  <si>
-    <t>2026</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1407,8 +1399,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2273,7 +2263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH69"/>
+  <dimension ref="A1:BH60"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
@@ -2301,48 +2291,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:60" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="150" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="153"/>
-      <c r="K1" s="153"/>
-      <c r="L1" s="153"/>
-      <c r="M1" s="153"/>
-      <c r="N1" s="153"/>
-      <c r="O1" s="153"/>
-      <c r="P1" s="153"/>
-      <c r="Q1" s="153"/>
-      <c r="R1" s="153"/>
-      <c r="S1" s="153"/>
-      <c r="T1" s="153"/>
-      <c r="U1" s="153"/>
-      <c r="V1" s="153"/>
-      <c r="W1" s="153"/>
-      <c r="X1" s="153"/>
-      <c r="Y1" s="153"/>
-      <c r="Z1" s="153"/>
-      <c r="AA1" s="153"/>
-      <c r="AB1" s="153"/>
-      <c r="AC1" s="153"/>
-      <c r="AD1" s="153"/>
-      <c r="AE1" s="153"/>
-      <c r="AF1" s="153"/>
-      <c r="AG1" s="153"/>
-      <c r="AH1" s="153"/>
-      <c r="AI1" s="153"/>
-      <c r="AU1" s="62"/>
-      <c r="AV1" s="62"/>
-      <c r="AW1" s="62"/>
-      <c r="AX1" s="62"/>
-      <c r="AY1" s="62"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
+      <c r="V1" s="151"/>
+      <c r="W1" s="151"/>
+      <c r="X1" s="151"/>
+      <c r="Y1" s="151"/>
+      <c r="Z1" s="151"/>
+      <c r="AA1" s="151"/>
+      <c r="AB1" s="151"/>
+      <c r="AC1" s="151"/>
+      <c r="AD1" s="151"/>
+      <c r="AE1" s="151"/>
+      <c r="AF1" s="151"/>
+      <c r="AG1" s="151"/>
+      <c r="AH1" s="151"/>
+      <c r="AI1" s="151"/>
+      <c r="AW1" s="35"/>
+      <c r="AX1" s="35"/>
+      <c r="AY1" s="35"/>
       <c r="AZ1" s="35"/>
       <c r="BA1" s="35"/>
       <c r="BB1" s="35"/>
@@ -2354,48 +2342,46 @@
       <c r="BH1" s="35"/>
     </row>
     <row r="2" spans="1:60" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="127" t="s">
         <v>171</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="130"/>
-      <c r="Q2" s="130"/>
-      <c r="R2" s="130"/>
-      <c r="S2" s="130"/>
-      <c r="T2" s="130"/>
-      <c r="U2" s="130"/>
-      <c r="V2" s="130"/>
-      <c r="W2" s="130"/>
-      <c r="X2" s="130"/>
-      <c r="Y2" s="130"/>
-      <c r="Z2" s="130"/>
-      <c r="AA2" s="130"/>
-      <c r="AB2" s="130"/>
-      <c r="AC2" s="130"/>
-      <c r="AD2" s="130"/>
-      <c r="AE2" s="130"/>
-      <c r="AF2" s="130"/>
-      <c r="AG2" s="130"/>
-      <c r="AH2" s="130"/>
-      <c r="AI2" s="130"/>
-      <c r="AU2" s="62"/>
-      <c r="AV2" s="62"/>
-      <c r="AW2" s="62"/>
-      <c r="AX2" s="62"/>
-      <c r="AY2" s="62"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="128"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="128"/>
+      <c r="R2" s="128"/>
+      <c r="S2" s="128"/>
+      <c r="T2" s="128"/>
+      <c r="U2" s="128"/>
+      <c r="V2" s="128"/>
+      <c r="W2" s="128"/>
+      <c r="X2" s="128"/>
+      <c r="Y2" s="128"/>
+      <c r="Z2" s="128"/>
+      <c r="AA2" s="128"/>
+      <c r="AB2" s="128"/>
+      <c r="AC2" s="128"/>
+      <c r="AD2" s="128"/>
+      <c r="AE2" s="128"/>
+      <c r="AF2" s="128"/>
+      <c r="AG2" s="128"/>
+      <c r="AH2" s="128"/>
+      <c r="AI2" s="128"/>
+      <c r="AW2" s="35"/>
+      <c r="AX2" s="35"/>
+      <c r="AY2" s="35"/>
       <c r="AZ2" s="35"/>
       <c r="BA2" s="35"/>
       <c r="BB2" s="35"/>
@@ -2407,46 +2393,44 @@
       <c r="BH2" s="35"/>
     </row>
     <row r="3" spans="1:60" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="130"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="130"/>
-      <c r="Q3" s="130"/>
-      <c r="R3" s="130"/>
-      <c r="S3" s="130"/>
-      <c r="T3" s="130"/>
-      <c r="U3" s="130"/>
-      <c r="V3" s="130"/>
-      <c r="W3" s="130"/>
-      <c r="X3" s="130"/>
-      <c r="Y3" s="130"/>
-      <c r="Z3" s="130"/>
-      <c r="AA3" s="130"/>
-      <c r="AB3" s="130"/>
-      <c r="AC3" s="130"/>
-      <c r="AD3" s="130"/>
-      <c r="AE3" s="130"/>
-      <c r="AF3" s="130"/>
-      <c r="AG3" s="130"/>
-      <c r="AH3" s="130"/>
-      <c r="AI3" s="130"/>
-      <c r="AU3" s="62"/>
-      <c r="AV3" s="62"/>
-      <c r="AW3" s="62"/>
-      <c r="AX3" s="62"/>
-      <c r="AY3" s="62"/>
+      <c r="A3" s="128"/>
+      <c r="B3" s="128"/>
+      <c r="C3" s="128"/>
+      <c r="D3" s="128"/>
+      <c r="E3" s="128"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="128"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="128"/>
+      <c r="R3" s="128"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="128"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="128"/>
+      <c r="Y3" s="128"/>
+      <c r="Z3" s="128"/>
+      <c r="AA3" s="128"/>
+      <c r="AB3" s="128"/>
+      <c r="AC3" s="128"/>
+      <c r="AD3" s="128"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="128"/>
+      <c r="AG3" s="128"/>
+      <c r="AH3" s="128"/>
+      <c r="AI3" s="128"/>
+      <c r="AW3" s="35"/>
+      <c r="AX3" s="35"/>
+      <c r="AY3" s="35"/>
       <c r="AZ3" s="35"/>
       <c r="BA3" s="35"/>
       <c r="BB3" s="35"/>
@@ -2458,46 +2442,44 @@
       <c r="BH3" s="35"/>
     </row>
     <row r="4" spans="1:60" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="131"/>
-      <c r="B4" s="131"/>
-      <c r="C4" s="131"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="131"/>
-      <c r="O4" s="131"/>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="131"/>
-      <c r="R4" s="131"/>
-      <c r="S4" s="131"/>
-      <c r="T4" s="131"/>
-      <c r="U4" s="131"/>
-      <c r="V4" s="131"/>
-      <c r="W4" s="131"/>
-      <c r="X4" s="131"/>
-      <c r="Y4" s="131"/>
-      <c r="Z4" s="131"/>
-      <c r="AA4" s="131"/>
-      <c r="AB4" s="131"/>
-      <c r="AC4" s="131"/>
-      <c r="AD4" s="131"/>
-      <c r="AE4" s="131"/>
-      <c r="AF4" s="131"/>
-      <c r="AG4" s="131"/>
-      <c r="AH4" s="131"/>
-      <c r="AI4" s="131"/>
-      <c r="AU4" s="62"/>
-      <c r="AV4" s="62"/>
-      <c r="AW4" s="62"/>
-      <c r="AX4" s="62"/>
-      <c r="AY4" s="62"/>
+      <c r="A4" s="129"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="129"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="129"/>
+      <c r="K4" s="129"/>
+      <c r="L4" s="129"/>
+      <c r="M4" s="129"/>
+      <c r="N4" s="129"/>
+      <c r="O4" s="129"/>
+      <c r="P4" s="129"/>
+      <c r="Q4" s="129"/>
+      <c r="R4" s="129"/>
+      <c r="S4" s="129"/>
+      <c r="T4" s="129"/>
+      <c r="U4" s="129"/>
+      <c r="V4" s="129"/>
+      <c r="W4" s="129"/>
+      <c r="X4" s="129"/>
+      <c r="Y4" s="129"/>
+      <c r="Z4" s="129"/>
+      <c r="AA4" s="129"/>
+      <c r="AB4" s="129"/>
+      <c r="AC4" s="129"/>
+      <c r="AD4" s="129"/>
+      <c r="AE4" s="129"/>
+      <c r="AF4" s="129"/>
+      <c r="AG4" s="129"/>
+      <c r="AH4" s="129"/>
+      <c r="AI4" s="129"/>
+      <c r="AW4" s="35"/>
+      <c r="AX4" s="35"/>
+      <c r="AY4" s="35"/>
       <c r="AZ4" s="35"/>
       <c r="BA4" s="35"/>
       <c r="BB4" s="35"/>
@@ -2509,48 +2491,46 @@
       <c r="BH4" s="35"/>
     </row>
     <row r="5" spans="1:60" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="137" t="s">
         <v>99</v>
       </c>
-      <c r="B5" s="139"/>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="139"/>
-      <c r="F5" s="139"/>
-      <c r="G5" s="139"/>
-      <c r="H5" s="139"/>
-      <c r="I5" s="139"/>
-      <c r="J5" s="139"/>
-      <c r="K5" s="139"/>
-      <c r="L5" s="139"/>
-      <c r="M5" s="139"/>
-      <c r="N5" s="139"/>
-      <c r="O5" s="139"/>
-      <c r="P5" s="139"/>
-      <c r="Q5" s="139"/>
-      <c r="R5" s="139"/>
-      <c r="S5" s="139"/>
-      <c r="T5" s="139"/>
-      <c r="U5" s="139"/>
-      <c r="V5" s="139"/>
-      <c r="W5" s="139"/>
-      <c r="X5" s="139"/>
-      <c r="Y5" s="139"/>
-      <c r="Z5" s="139"/>
-      <c r="AA5" s="139"/>
-      <c r="AB5" s="139"/>
-      <c r="AC5" s="139"/>
-      <c r="AD5" s="139"/>
-      <c r="AE5" s="139"/>
-      <c r="AF5" s="139"/>
-      <c r="AG5" s="139"/>
-      <c r="AH5" s="139"/>
-      <c r="AI5" s="139"/>
-      <c r="AU5" s="62"/>
-      <c r="AV5" s="62"/>
-      <c r="AW5" s="62"/>
-      <c r="AX5" s="62"/>
-      <c r="AY5" s="62"/>
+      <c r="B5" s="137"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="137"/>
+      <c r="K5" s="137"/>
+      <c r="L5" s="137"/>
+      <c r="M5" s="137"/>
+      <c r="N5" s="137"/>
+      <c r="O5" s="137"/>
+      <c r="P5" s="137"/>
+      <c r="Q5" s="137"/>
+      <c r="R5" s="137"/>
+      <c r="S5" s="137"/>
+      <c r="T5" s="137"/>
+      <c r="U5" s="137"/>
+      <c r="V5" s="137"/>
+      <c r="W5" s="137"/>
+      <c r="X5" s="137"/>
+      <c r="Y5" s="137"/>
+      <c r="Z5" s="137"/>
+      <c r="AA5" s="137"/>
+      <c r="AB5" s="137"/>
+      <c r="AC5" s="137"/>
+      <c r="AD5" s="137"/>
+      <c r="AE5" s="137"/>
+      <c r="AF5" s="137"/>
+      <c r="AG5" s="137"/>
+      <c r="AH5" s="137"/>
+      <c r="AI5" s="137"/>
+      <c r="AW5" s="35"/>
+      <c r="AX5" s="35"/>
+      <c r="AY5" s="35"/>
       <c r="AZ5" s="35"/>
       <c r="BA5" s="35"/>
       <c r="BB5" s="35"/>
@@ -2562,46 +2542,44 @@
       <c r="BH5" s="35"/>
     </row>
     <row r="6" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A6" s="140"/>
-      <c r="B6" s="140"/>
-      <c r="C6" s="140"/>
-      <c r="D6" s="140"/>
-      <c r="E6" s="140"/>
-      <c r="F6" s="140"/>
-      <c r="G6" s="140"/>
-      <c r="H6" s="140"/>
-      <c r="I6" s="140"/>
-      <c r="J6" s="140"/>
-      <c r="K6" s="140"/>
-      <c r="L6" s="140"/>
-      <c r="M6" s="140"/>
-      <c r="N6" s="140"/>
-      <c r="O6" s="140"/>
-      <c r="P6" s="140"/>
-      <c r="Q6" s="140"/>
-      <c r="R6" s="140"/>
-      <c r="S6" s="140"/>
-      <c r="T6" s="140"/>
-      <c r="U6" s="140"/>
-      <c r="V6" s="140"/>
-      <c r="W6" s="140"/>
-      <c r="X6" s="140"/>
-      <c r="Y6" s="140"/>
-      <c r="Z6" s="140"/>
-      <c r="AA6" s="140"/>
-      <c r="AB6" s="140"/>
-      <c r="AC6" s="140"/>
-      <c r="AD6" s="140"/>
-      <c r="AE6" s="140"/>
-      <c r="AF6" s="140"/>
-      <c r="AG6" s="140"/>
-      <c r="AH6" s="140"/>
-      <c r="AI6" s="140"/>
-      <c r="AU6" s="62"/>
-      <c r="AV6" s="62"/>
-      <c r="AW6" s="62"/>
-      <c r="AX6" s="62"/>
-      <c r="AY6" s="62"/>
+      <c r="A6" s="138"/>
+      <c r="B6" s="138"/>
+      <c r="C6" s="138"/>
+      <c r="D6" s="138"/>
+      <c r="E6" s="138"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="138"/>
+      <c r="H6" s="138"/>
+      <c r="I6" s="138"/>
+      <c r="J6" s="138"/>
+      <c r="K6" s="138"/>
+      <c r="L6" s="138"/>
+      <c r="M6" s="138"/>
+      <c r="N6" s="138"/>
+      <c r="O6" s="138"/>
+      <c r="P6" s="138"/>
+      <c r="Q6" s="138"/>
+      <c r="R6" s="138"/>
+      <c r="S6" s="138"/>
+      <c r="T6" s="138"/>
+      <c r="U6" s="138"/>
+      <c r="V6" s="138"/>
+      <c r="W6" s="138"/>
+      <c r="X6" s="138"/>
+      <c r="Y6" s="138"/>
+      <c r="Z6" s="138"/>
+      <c r="AA6" s="138"/>
+      <c r="AB6" s="138"/>
+      <c r="AC6" s="138"/>
+      <c r="AD6" s="138"/>
+      <c r="AE6" s="138"/>
+      <c r="AF6" s="138"/>
+      <c r="AG6" s="138"/>
+      <c r="AH6" s="138"/>
+      <c r="AI6" s="138"/>
+      <c r="AW6" s="35"/>
+      <c r="AX6" s="35"/>
+      <c r="AY6" s="35"/>
       <c r="AZ6" s="35"/>
       <c r="BA6" s="35"/>
       <c r="BB6" s="35"/>
@@ -2616,34 +2594,34 @@
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="122" t="s">
+      <c r="B7" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="122"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="122"/>
-      <c r="N7" s="122"/>
-      <c r="O7" s="173"/>
-      <c r="P7" s="174"/>
-      <c r="Q7" s="174"/>
-      <c r="R7" s="174"/>
-      <c r="S7" s="174"/>
-      <c r="T7" s="174"/>
-      <c r="U7" s="174"/>
-      <c r="V7" s="174"/>
-      <c r="W7" s="175"/>
-      <c r="X7" s="176" t="s">
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="120"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="120"/>
+      <c r="K7" s="120"/>
+      <c r="L7" s="120"/>
+      <c r="M7" s="120"/>
+      <c r="N7" s="120"/>
+      <c r="O7" s="171"/>
+      <c r="P7" s="172"/>
+      <c r="Q7" s="172"/>
+      <c r="R7" s="172"/>
+      <c r="S7" s="172"/>
+      <c r="T7" s="172"/>
+      <c r="U7" s="172"/>
+      <c r="V7" s="172"/>
+      <c r="W7" s="173"/>
+      <c r="X7" s="174" t="s">
         <v>169</v>
       </c>
-      <c r="Y7" s="176"/>
+      <c r="Y7" s="174"/>
       <c r="Z7" s="56"/>
       <c r="AA7" s="57"/>
       <c r="AB7" s="58"/>
@@ -2654,11 +2632,9 @@
       <c r="AG7" s="59"/>
       <c r="AH7" s="58"/>
       <c r="AI7" s="60"/>
-      <c r="AU7" s="62"/>
-      <c r="AV7" s="62"/>
-      <c r="AW7" s="62"/>
-      <c r="AX7" s="62"/>
-      <c r="AY7" s="62"/>
+      <c r="AW7" s="35"/>
+      <c r="AX7" s="35"/>
+      <c r="AY7" s="35"/>
       <c r="AZ7" s="35"/>
       <c r="BA7" s="35"/>
       <c r="BB7" s="35"/>
@@ -2670,34 +2646,32 @@
       <c r="BH7" s="35"/>
     </row>
     <row r="8" spans="1:60" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O8" s="69" t="s">
+      <c r="O8" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="P8" s="69"/>
-      <c r="Q8" s="69"/>
-      <c r="R8" s="69"/>
-      <c r="S8" s="69"/>
-      <c r="T8" s="69"/>
-      <c r="U8" s="69"/>
-      <c r="V8" s="69"/>
-      <c r="W8" s="69"/>
-      <c r="X8" s="69"/>
-      <c r="Y8" s="69"/>
-      <c r="Z8" s="69"/>
-      <c r="AA8" s="69"/>
-      <c r="AB8" s="69"/>
-      <c r="AC8" s="69"/>
-      <c r="AD8" s="69"/>
-      <c r="AE8" s="69"/>
-      <c r="AF8" s="69"/>
-      <c r="AG8" s="69"/>
-      <c r="AH8" s="69"/>
-      <c r="AI8" s="69"/>
-      <c r="AU8" s="62"/>
-      <c r="AV8" s="62"/>
-      <c r="AW8" s="62"/>
-      <c r="AX8" s="62"/>
-      <c r="AY8" s="62"/>
+      <c r="P8" s="67"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="67"/>
+      <c r="T8" s="67"/>
+      <c r="U8" s="67"/>
+      <c r="V8" s="67"/>
+      <c r="W8" s="67"/>
+      <c r="X8" s="67"/>
+      <c r="Y8" s="67"/>
+      <c r="Z8" s="67"/>
+      <c r="AA8" s="67"/>
+      <c r="AB8" s="67"/>
+      <c r="AC8" s="67"/>
+      <c r="AD8" s="67"/>
+      <c r="AE8" s="67"/>
+      <c r="AF8" s="67"/>
+      <c r="AG8" s="67"/>
+      <c r="AH8" s="67"/>
+      <c r="AI8" s="67"/>
+      <c r="AW8" s="35"/>
+      <c r="AX8" s="35"/>
+      <c r="AY8" s="35"/>
       <c r="AZ8" s="35"/>
       <c r="BA8" s="35"/>
       <c r="BB8" s="35"/>
@@ -2712,34 +2686,34 @@
       <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="120" t="s">
+      <c r="B9" s="118" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="173"/>
-      <c r="L9" s="174"/>
-      <c r="M9" s="174"/>
-      <c r="N9" s="174"/>
-      <c r="O9" s="174"/>
-      <c r="P9" s="174"/>
-      <c r="Q9" s="174"/>
-      <c r="R9" s="174"/>
-      <c r="S9" s="174"/>
-      <c r="T9" s="174"/>
-      <c r="U9" s="174"/>
-      <c r="V9" s="174"/>
-      <c r="W9" s="175"/>
-      <c r="X9" s="176" t="s">
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="171"/>
+      <c r="L9" s="172"/>
+      <c r="M9" s="172"/>
+      <c r="N9" s="172"/>
+      <c r="O9" s="172"/>
+      <c r="P9" s="172"/>
+      <c r="Q9" s="172"/>
+      <c r="R9" s="172"/>
+      <c r="S9" s="172"/>
+      <c r="T9" s="172"/>
+      <c r="U9" s="172"/>
+      <c r="V9" s="172"/>
+      <c r="W9" s="173"/>
+      <c r="X9" s="174" t="s">
         <v>169</v>
       </c>
-      <c r="Y9" s="176"/>
+      <c r="Y9" s="174"/>
       <c r="Z9" s="56"/>
       <c r="AA9" s="57"/>
       <c r="AB9" s="58"/>
@@ -2750,11 +2724,9 @@
       <c r="AG9" s="59"/>
       <c r="AH9" s="58"/>
       <c r="AI9" s="60"/>
-      <c r="AU9" s="62"/>
-      <c r="AV9" s="62"/>
-      <c r="AW9" s="62"/>
-      <c r="AX9" s="62"/>
-      <c r="AY9" s="62"/>
+      <c r="AW9" s="35"/>
+      <c r="AX9" s="35"/>
+      <c r="AY9" s="35"/>
       <c r="AZ9" s="35"/>
       <c r="BA9" s="35"/>
       <c r="BB9" s="35"/>
@@ -2766,39 +2738,37 @@
       <c r="BH9" s="35"/>
     </row>
     <row r="10" spans="1:60" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J10" s="69" t="s">
+      <c r="J10" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="K10" s="69"/>
-      <c r="L10" s="69"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="69"/>
-      <c r="O10" s="69"/>
-      <c r="P10" s="69"/>
-      <c r="Q10" s="69"/>
-      <c r="R10" s="69"/>
-      <c r="S10" s="69"/>
-      <c r="T10" s="69"/>
-      <c r="U10" s="69"/>
-      <c r="V10" s="69"/>
-      <c r="W10" s="69"/>
-      <c r="X10" s="69"/>
-      <c r="Y10" s="69"/>
-      <c r="Z10" s="69"/>
-      <c r="AA10" s="69"/>
-      <c r="AB10" s="69"/>
-      <c r="AC10" s="69"/>
-      <c r="AD10" s="69"/>
-      <c r="AE10" s="69"/>
-      <c r="AF10" s="69"/>
-      <c r="AG10" s="69"/>
-      <c r="AH10" s="69"/>
-      <c r="AI10" s="69"/>
-      <c r="AU10" s="62"/>
-      <c r="AV10" s="62"/>
-      <c r="AW10" s="62"/>
-      <c r="AX10" s="62"/>
-      <c r="AY10" s="62"/>
+      <c r="K10" s="67"/>
+      <c r="L10" s="67"/>
+      <c r="M10" s="67"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="67"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="67"/>
+      <c r="T10" s="67"/>
+      <c r="U10" s="67"/>
+      <c r="V10" s="67"/>
+      <c r="W10" s="67"/>
+      <c r="X10" s="67"/>
+      <c r="Y10" s="67"/>
+      <c r="Z10" s="67"/>
+      <c r="AA10" s="67"/>
+      <c r="AB10" s="67"/>
+      <c r="AC10" s="67"/>
+      <c r="AD10" s="67"/>
+      <c r="AE10" s="67"/>
+      <c r="AF10" s="67"/>
+      <c r="AG10" s="67"/>
+      <c r="AH10" s="67"/>
+      <c r="AI10" s="67"/>
+      <c r="AW10" s="35"/>
+      <c r="AX10" s="35"/>
+      <c r="AY10" s="35"/>
       <c r="AZ10" s="35"/>
       <c r="BA10" s="35"/>
       <c r="BB10" s="35"/>
@@ -2813,47 +2783,45 @@
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="142" t="s">
+      <c r="B11" s="140" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="142"/>
-      <c r="D11" s="142"/>
-      <c r="E11" s="142"/>
-      <c r="F11" s="143"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="144"/>
-      <c r="L11" s="144"/>
-      <c r="M11" s="144"/>
-      <c r="N11" s="144"/>
-      <c r="O11" s="144"/>
-      <c r="P11" s="144"/>
-      <c r="Q11" s="144"/>
-      <c r="R11" s="144"/>
-      <c r="S11" s="144"/>
-      <c r="T11" s="144"/>
-      <c r="U11" s="144"/>
-      <c r="V11" s="144"/>
-      <c r="W11" s="144"/>
-      <c r="X11" s="144"/>
-      <c r="Y11" s="144"/>
-      <c r="Z11" s="144"/>
-      <c r="AA11" s="144"/>
-      <c r="AB11" s="144"/>
-      <c r="AC11" s="144"/>
-      <c r="AD11" s="144"/>
-      <c r="AE11" s="144"/>
-      <c r="AF11" s="144"/>
-      <c r="AG11" s="144"/>
-      <c r="AH11" s="145"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="141"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="142"/>
+      <c r="L11" s="142"/>
+      <c r="M11" s="142"/>
+      <c r="N11" s="142"/>
+      <c r="O11" s="142"/>
+      <c r="P11" s="142"/>
+      <c r="Q11" s="142"/>
+      <c r="R11" s="142"/>
+      <c r="S11" s="142"/>
+      <c r="T11" s="142"/>
+      <c r="U11" s="142"/>
+      <c r="V11" s="142"/>
+      <c r="W11" s="142"/>
+      <c r="X11" s="142"/>
+      <c r="Y11" s="142"/>
+      <c r="Z11" s="142"/>
+      <c r="AA11" s="142"/>
+      <c r="AB11" s="142"/>
+      <c r="AC11" s="142"/>
+      <c r="AD11" s="142"/>
+      <c r="AE11" s="142"/>
+      <c r="AF11" s="142"/>
+      <c r="AG11" s="142"/>
+      <c r="AH11" s="143"/>
       <c r="AI11" s="14"/>
-      <c r="AU11" s="62"/>
-      <c r="AV11" s="62"/>
-      <c r="AW11" s="62"/>
-      <c r="AX11" s="62"/>
-      <c r="AY11" s="62"/>
+      <c r="AW11" s="35"/>
+      <c r="AX11" s="35"/>
+      <c r="AY11" s="35"/>
       <c r="AZ11" s="35"/>
       <c r="BA11" s="35"/>
       <c r="BB11" s="35"/>
@@ -2865,43 +2833,41 @@
       <c r="BH11" s="35"/>
     </row>
     <row r="12" spans="1:60" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F12" s="69" t="s">
+      <c r="F12" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="69"/>
-      <c r="H12" s="69"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="69"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="69"/>
-      <c r="O12" s="69"/>
-      <c r="P12" s="69"/>
-      <c r="Q12" s="69"/>
-      <c r="R12" s="69"/>
-      <c r="S12" s="69"/>
-      <c r="T12" s="69"/>
-      <c r="U12" s="69"/>
-      <c r="V12" s="69"/>
-      <c r="W12" s="69"/>
-      <c r="X12" s="69"/>
-      <c r="Y12" s="69"/>
-      <c r="Z12" s="69"/>
-      <c r="AA12" s="69"/>
-      <c r="AB12" s="69"/>
-      <c r="AC12" s="69"/>
-      <c r="AD12" s="69"/>
-      <c r="AE12" s="69"/>
-      <c r="AF12" s="69"/>
-      <c r="AG12" s="69"/>
-      <c r="AH12" s="69"/>
-      <c r="AI12" s="69"/>
-      <c r="AU12" s="62"/>
-      <c r="AV12" s="62"/>
-      <c r="AW12" s="62"/>
-      <c r="AX12" s="62"/>
-      <c r="AY12" s="62"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="67"/>
+      <c r="N12" s="67"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="67"/>
+      <c r="T12" s="67"/>
+      <c r="U12" s="67"/>
+      <c r="V12" s="67"/>
+      <c r="W12" s="67"/>
+      <c r="X12" s="67"/>
+      <c r="Y12" s="67"/>
+      <c r="Z12" s="67"/>
+      <c r="AA12" s="67"/>
+      <c r="AB12" s="67"/>
+      <c r="AC12" s="67"/>
+      <c r="AD12" s="67"/>
+      <c r="AE12" s="67"/>
+      <c r="AF12" s="67"/>
+      <c r="AG12" s="67"/>
+      <c r="AH12" s="67"/>
+      <c r="AI12" s="67"/>
+      <c r="AW12" s="35"/>
+      <c r="AX12" s="35"/>
+      <c r="AY12" s="35"/>
       <c r="AZ12" s="35"/>
       <c r="BA12" s="35"/>
       <c r="BB12" s="35"/>
@@ -2913,47 +2879,45 @@
       <c r="BH12" s="35"/>
     </row>
     <row r="13" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B13" s="120" t="s">
+      <c r="B13" s="118" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="120"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="120"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="120"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="146"/>
-      <c r="J13" s="147"/>
-      <c r="K13" s="147"/>
-      <c r="L13" s="147"/>
-      <c r="M13" s="147"/>
-      <c r="N13" s="147"/>
-      <c r="O13" s="147"/>
-      <c r="P13" s="147"/>
-      <c r="Q13" s="147"/>
-      <c r="R13" s="147"/>
-      <c r="S13" s="147"/>
-      <c r="T13" s="147"/>
-      <c r="U13" s="147"/>
-      <c r="V13" s="147"/>
-      <c r="W13" s="147"/>
-      <c r="X13" s="147"/>
-      <c r="Y13" s="147"/>
-      <c r="Z13" s="147"/>
-      <c r="AA13" s="147"/>
-      <c r="AB13" s="147"/>
-      <c r="AC13" s="147"/>
-      <c r="AD13" s="147"/>
-      <c r="AE13" s="147"/>
-      <c r="AF13" s="147"/>
-      <c r="AG13" s="147"/>
-      <c r="AH13" s="147"/>
-      <c r="AI13" s="148"/>
-      <c r="AU13" s="62"/>
-      <c r="AV13" s="62"/>
-      <c r="AW13" s="62"/>
-      <c r="AX13" s="62"/>
-      <c r="AY13" s="62"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="118"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="133"/>
+      <c r="I13" s="144"/>
+      <c r="J13" s="145"/>
+      <c r="K13" s="145"/>
+      <c r="L13" s="145"/>
+      <c r="M13" s="145"/>
+      <c r="N13" s="145"/>
+      <c r="O13" s="145"/>
+      <c r="P13" s="145"/>
+      <c r="Q13" s="145"/>
+      <c r="R13" s="145"/>
+      <c r="S13" s="145"/>
+      <c r="T13" s="145"/>
+      <c r="U13" s="145"/>
+      <c r="V13" s="145"/>
+      <c r="W13" s="145"/>
+      <c r="X13" s="145"/>
+      <c r="Y13" s="145"/>
+      <c r="Z13" s="145"/>
+      <c r="AA13" s="145"/>
+      <c r="AB13" s="145"/>
+      <c r="AC13" s="145"/>
+      <c r="AD13" s="145"/>
+      <c r="AE13" s="145"/>
+      <c r="AF13" s="145"/>
+      <c r="AG13" s="145"/>
+      <c r="AH13" s="145"/>
+      <c r="AI13" s="146"/>
+      <c r="AW13" s="35"/>
+      <c r="AX13" s="35"/>
+      <c r="AY13" s="35"/>
       <c r="AZ13" s="35"/>
       <c r="BA13" s="35"/>
       <c r="BB13" s="35"/>
@@ -2968,39 +2932,37 @@
       <c r="F14" s="11"/>
       <c r="G14" s="11"/>
       <c r="H14" s="11"/>
-      <c r="I14" s="149"/>
-      <c r="J14" s="150"/>
-      <c r="K14" s="150"/>
-      <c r="L14" s="150"/>
-      <c r="M14" s="150"/>
-      <c r="N14" s="150"/>
-      <c r="O14" s="150"/>
-      <c r="P14" s="150"/>
-      <c r="Q14" s="150"/>
-      <c r="R14" s="150"/>
-      <c r="S14" s="150"/>
-      <c r="T14" s="150"/>
-      <c r="U14" s="150"/>
-      <c r="V14" s="150"/>
-      <c r="W14" s="150"/>
-      <c r="X14" s="150"/>
-      <c r="Y14" s="150"/>
-      <c r="Z14" s="150"/>
-      <c r="AA14" s="150"/>
-      <c r="AB14" s="150"/>
-      <c r="AC14" s="150"/>
-      <c r="AD14" s="150"/>
-      <c r="AE14" s="150"/>
-      <c r="AF14" s="150"/>
-      <c r="AG14" s="150"/>
-      <c r="AH14" s="150"/>
-      <c r="AI14" s="151"/>
+      <c r="I14" s="147"/>
+      <c r="J14" s="148"/>
+      <c r="K14" s="148"/>
+      <c r="L14" s="148"/>
+      <c r="M14" s="148"/>
+      <c r="N14" s="148"/>
+      <c r="O14" s="148"/>
+      <c r="P14" s="148"/>
+      <c r="Q14" s="148"/>
+      <c r="R14" s="148"/>
+      <c r="S14" s="148"/>
+      <c r="T14" s="148"/>
+      <c r="U14" s="148"/>
+      <c r="V14" s="148"/>
+      <c r="W14" s="148"/>
+      <c r="X14" s="148"/>
+      <c r="Y14" s="148"/>
+      <c r="Z14" s="148"/>
+      <c r="AA14" s="148"/>
+      <c r="AB14" s="148"/>
+      <c r="AC14" s="148"/>
+      <c r="AD14" s="148"/>
+      <c r="AE14" s="148"/>
+      <c r="AF14" s="148"/>
+      <c r="AG14" s="148"/>
+      <c r="AH14" s="148"/>
+      <c r="AI14" s="149"/>
       <c r="AP14" s="38"/>
-      <c r="AU14" s="62"/>
-      <c r="AV14" s="62"/>
-      <c r="AW14" s="62"/>
-      <c r="AX14" s="62"/>
-      <c r="AY14" s="62"/>
+      <c r="AW14" s="35"/>
+      <c r="AX14" s="35"/>
+      <c r="AY14" s="35"/>
       <c r="AZ14" s="35"/>
       <c r="BA14" s="35"/>
       <c r="BB14" s="35"/>
@@ -3012,41 +2974,39 @@
       <c r="BH14" s="35"/>
     </row>
     <row r="15" spans="1:60" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I15" s="97" t="s">
+      <c r="I15" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="J15" s="97"/>
-      <c r="K15" s="97"/>
-      <c r="L15" s="97"/>
-      <c r="M15" s="97"/>
-      <c r="N15" s="97"/>
-      <c r="O15" s="97"/>
-      <c r="P15" s="97"/>
-      <c r="Q15" s="97"/>
-      <c r="R15" s="97"/>
-      <c r="S15" s="97"/>
-      <c r="T15" s="97"/>
-      <c r="U15" s="97"/>
-      <c r="V15" s="97"/>
-      <c r="W15" s="97"/>
-      <c r="X15" s="97"/>
-      <c r="Y15" s="97"/>
-      <c r="Z15" s="97"/>
-      <c r="AA15" s="97"/>
-      <c r="AB15" s="97"/>
-      <c r="AC15" s="97"/>
-      <c r="AD15" s="97"/>
-      <c r="AE15" s="97"/>
-      <c r="AF15" s="97"/>
-      <c r="AG15" s="97"/>
-      <c r="AH15" s="97"/>
-      <c r="AI15" s="97"/>
+      <c r="J15" s="95"/>
+      <c r="K15" s="95"/>
+      <c r="L15" s="95"/>
+      <c r="M15" s="95"/>
+      <c r="N15" s="95"/>
+      <c r="O15" s="95"/>
+      <c r="P15" s="95"/>
+      <c r="Q15" s="95"/>
+      <c r="R15" s="95"/>
+      <c r="S15" s="95"/>
+      <c r="T15" s="95"/>
+      <c r="U15" s="95"/>
+      <c r="V15" s="95"/>
+      <c r="W15" s="95"/>
+      <c r="X15" s="95"/>
+      <c r="Y15" s="95"/>
+      <c r="Z15" s="95"/>
+      <c r="AA15" s="95"/>
+      <c r="AB15" s="95"/>
+      <c r="AC15" s="95"/>
+      <c r="AD15" s="95"/>
+      <c r="AE15" s="95"/>
+      <c r="AF15" s="95"/>
+      <c r="AG15" s="95"/>
+      <c r="AH15" s="95"/>
+      <c r="AI15" s="95"/>
       <c r="AP15" s="38"/>
-      <c r="AU15" s="62"/>
-      <c r="AV15" s="62"/>
-      <c r="AW15" s="62"/>
-      <c r="AX15" s="62"/>
-      <c r="AY15" s="62"/>
+      <c r="AW15" s="35"/>
+      <c r="AX15" s="35"/>
+      <c r="AY15" s="35"/>
       <c r="AZ15" s="35"/>
       <c r="BA15" s="35"/>
       <c r="BB15" s="35"/>
@@ -3061,33 +3021,31 @@
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="122" t="s">
+      <c r="B16" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="122"/>
-      <c r="I16" s="122"/>
-      <c r="J16" s="122"/>
-      <c r="K16" s="122"/>
-      <c r="L16" s="122"/>
-      <c r="M16" s="122"/>
-      <c r="N16" s="122"/>
-      <c r="O16" s="122"/>
-      <c r="P16" s="122"/>
-      <c r="Q16" s="135"/>
-      <c r="R16" s="136"/>
-      <c r="S16" s="137"/>
-      <c r="T16" s="138"/>
+      <c r="C16" s="120"/>
+      <c r="D16" s="120"/>
+      <c r="E16" s="120"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="120"/>
+      <c r="H16" s="120"/>
+      <c r="I16" s="120"/>
+      <c r="J16" s="120"/>
+      <c r="K16" s="120"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="120"/>
+      <c r="Q16" s="133"/>
+      <c r="R16" s="134"/>
+      <c r="S16" s="135"/>
+      <c r="T16" s="136"/>
       <c r="AP16" s="38"/>
-      <c r="AU16" s="62"/>
-      <c r="AV16" s="62"/>
-      <c r="AW16" s="62"/>
-      <c r="AX16" s="62"/>
-      <c r="AY16" s="62"/>
+      <c r="AW16" s="35"/>
+      <c r="AX16" s="35"/>
+      <c r="AY16" s="35"/>
       <c r="AZ16" s="35"/>
       <c r="BA16" s="35"/>
       <c r="BB16" s="35"/>
@@ -3100,11 +3058,9 @@
     </row>
     <row r="17" spans="1:60" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AP17" s="38"/>
-      <c r="AU17" s="62"/>
-      <c r="AV17" s="62"/>
-      <c r="AW17" s="62"/>
-      <c r="AX17" s="62"/>
-      <c r="AY17" s="62"/>
+      <c r="AW17" s="35"/>
+      <c r="AX17" s="35"/>
+      <c r="AY17" s="35"/>
       <c r="AZ17" s="35"/>
       <c r="BA17" s="35"/>
       <c r="BB17" s="35"/>
@@ -3119,52 +3075,50 @@
       <c r="A18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="122" t="s">
+      <c r="B18" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="122"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="122"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="122"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="122"/>
-      <c r="N18" s="122"/>
-      <c r="O18" s="122"/>
-      <c r="P18" s="122"/>
-      <c r="Q18" s="132"/>
-      <c r="R18" s="133"/>
-      <c r="S18" s="133"/>
-      <c r="T18" s="133"/>
-      <c r="U18" s="133"/>
-      <c r="V18" s="134"/>
+      <c r="C18" s="120"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="120"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="120"/>
+      <c r="K18" s="120"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="120"/>
+      <c r="N18" s="120"/>
+      <c r="O18" s="120"/>
+      <c r="P18" s="120"/>
+      <c r="Q18" s="130"/>
+      <c r="R18" s="131"/>
+      <c r="S18" s="131"/>
+      <c r="T18" s="131"/>
+      <c r="U18" s="131"/>
+      <c r="V18" s="132"/>
       <c r="W18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="X18" s="88"/>
-      <c r="Y18" s="89"/>
-      <c r="Z18" s="90"/>
-      <c r="AA18" s="89"/>
-      <c r="AB18" s="90"/>
-      <c r="AC18" s="91"/>
+      <c r="X18" s="86"/>
+      <c r="Y18" s="87"/>
+      <c r="Z18" s="88"/>
+      <c r="AA18" s="87"/>
+      <c r="AB18" s="88"/>
+      <c r="AC18" s="89"/>
       <c r="AD18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AE18" s="79"/>
-      <c r="AF18" s="80"/>
-      <c r="AG18" s="80"/>
-      <c r="AH18" s="80"/>
-      <c r="AI18" s="81"/>
+      <c r="AE18" s="77"/>
+      <c r="AF18" s="78"/>
+      <c r="AG18" s="78"/>
+      <c r="AH18" s="78"/>
+      <c r="AI18" s="79"/>
       <c r="AP18" s="38"/>
-      <c r="AU18" s="62"/>
-      <c r="AV18" s="62"/>
-      <c r="AW18" s="62"/>
-      <c r="AX18" s="62"/>
-      <c r="AY18" s="62"/>
+      <c r="AW18" s="35"/>
+      <c r="AX18" s="35"/>
+      <c r="AY18" s="35"/>
       <c r="AZ18" s="35"/>
       <c r="BA18" s="35"/>
       <c r="BB18" s="35"/>
@@ -3176,51 +3130,51 @@
       <c r="BH18" s="35"/>
     </row>
     <row r="19" spans="1:60" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="69" t="s">
+      <c r="B19" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="69"/>
-      <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="69"/>
-      <c r="M19" s="69"/>
-      <c r="N19" s="69"/>
-      <c r="O19" s="69"/>
-      <c r="P19" s="69"/>
-      <c r="Q19" s="69" t="s">
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="67"/>
+      <c r="J19" s="67"/>
+      <c r="K19" s="67"/>
+      <c r="L19" s="67"/>
+      <c r="M19" s="67"/>
+      <c r="N19" s="67"/>
+      <c r="O19" s="67"/>
+      <c r="P19" s="67"/>
+      <c r="Q19" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="R19" s="69"/>
-      <c r="S19" s="69"/>
-      <c r="T19" s="69"/>
-      <c r="U19" s="69"/>
-      <c r="V19" s="69"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="67"/>
+      <c r="T19" s="67"/>
+      <c r="U19" s="67"/>
+      <c r="V19" s="67"/>
       <c r="W19" s="3"/>
-      <c r="X19" s="99" t="s">
+      <c r="X19" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="Y19" s="99"/>
-      <c r="Z19" s="99" t="s">
+      <c r="Y19" s="97"/>
+      <c r="Z19" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="AA19" s="99"/>
-      <c r="AB19" s="99" t="s">
+      <c r="AA19" s="97"/>
+      <c r="AB19" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="AC19" s="99"/>
-      <c r="AE19" s="104" t="s">
+      <c r="AC19" s="97"/>
+      <c r="AE19" s="102" t="s">
         <v>13</v>
       </c>
-      <c r="AF19" s="104"/>
-      <c r="AG19" s="104"/>
-      <c r="AH19" s="104"/>
-      <c r="AI19" s="104"/>
+      <c r="AF19" s="102"/>
+      <c r="AG19" s="102"/>
+      <c r="AH19" s="102"/>
+      <c r="AI19" s="102"/>
       <c r="AJ19" s="39"/>
       <c r="AO19" s="38" t="s">
         <v>65</v>
@@ -3237,11 +3191,9 @@
       <c r="AS19" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="AU19" s="62"/>
-      <c r="AV19" s="62"/>
-      <c r="AW19" s="62"/>
-      <c r="AX19" s="62"/>
-      <c r="AY19" s="62"/>
+      <c r="AW19" s="35"/>
+      <c r="AX19" s="35"/>
+      <c r="AY19" s="35"/>
       <c r="AZ19" s="35"/>
       <c r="BA19" s="35"/>
       <c r="BB19" s="35"/>
@@ -3256,19 +3208,19 @@
       <c r="A20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="122" t="s">
+      <c r="B20" s="120" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="122"/>
-      <c r="D20" s="122"/>
-      <c r="E20" s="122"/>
-      <c r="F20" s="122"/>
-      <c r="G20" s="122"/>
-      <c r="H20" s="122"/>
-      <c r="I20" s="122"/>
-      <c r="J20" s="122"/>
-      <c r="K20" s="122"/>
-      <c r="L20" s="122"/>
+      <c r="C20" s="120"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="120"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="120"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="120"/>
+      <c r="K20" s="120"/>
+      <c r="L20" s="120"/>
       <c r="M20" s="4"/>
       <c r="X20" s="21"/>
       <c r="Y20" s="21"/>
@@ -3276,11 +3228,11 @@
       <c r="AA20" s="21"/>
       <c r="AB20" s="21"/>
       <c r="AC20" s="21"/>
-      <c r="AE20" s="104"/>
-      <c r="AF20" s="104"/>
-      <c r="AG20" s="104"/>
-      <c r="AH20" s="104"/>
-      <c r="AI20" s="104"/>
+      <c r="AE20" s="102"/>
+      <c r="AF20" s="102"/>
+      <c r="AG20" s="102"/>
+      <c r="AH20" s="102"/>
+      <c r="AI20" s="102"/>
       <c r="AJ20" s="40" t="s">
         <v>62</v>
       </c>
@@ -3302,11 +3254,9 @@
       <c r="AS20" s="37" t="s">
         <v>108</v>
       </c>
-      <c r="AU20" s="62"/>
-      <c r="AV20" s="62"/>
-      <c r="AW20" s="62"/>
-      <c r="AX20" s="62"/>
-      <c r="AY20" s="62"/>
+      <c r="AW20" s="35"/>
+      <c r="AX20" s="35"/>
+      <c r="AY20" s="35"/>
       <c r="AZ20" s="35"/>
       <c r="BA20" s="35"/>
       <c r="BB20" s="35"/>
@@ -3318,47 +3268,47 @@
       <c r="BH20" s="35"/>
     </row>
     <row r="21" spans="1:60" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="141" t="s">
+      <c r="C21" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="141"/>
-      <c r="E21" s="141"/>
-      <c r="F21" s="141"/>
-      <c r="G21" s="141"/>
-      <c r="H21" s="141"/>
-      <c r="J21" s="123" t="s">
+      <c r="D21" s="139"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="139"/>
+      <c r="J21" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="K21" s="123"/>
-      <c r="L21" s="123"/>
-      <c r="M21" s="123"/>
-      <c r="N21" s="123" t="s">
+      <c r="K21" s="121"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121" t="s">
         <v>96</v>
       </c>
-      <c r="O21" s="123"/>
-      <c r="P21" s="123"/>
-      <c r="Q21" s="123"/>
+      <c r="O21" s="121"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="121"/>
       <c r="R21" s="23"/>
-      <c r="U21" s="141" t="s">
+      <c r="U21" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="V21" s="141"/>
-      <c r="W21" s="141"/>
-      <c r="X21" s="141"/>
-      <c r="Y21" s="141"/>
-      <c r="Z21" s="141"/>
-      <c r="AB21" s="123" t="s">
+      <c r="V21" s="139"/>
+      <c r="W21" s="139"/>
+      <c r="X21" s="139"/>
+      <c r="Y21" s="139"/>
+      <c r="Z21" s="139"/>
+      <c r="AB21" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="AC21" s="123"/>
-      <c r="AD21" s="123"/>
-      <c r="AE21" s="123"/>
-      <c r="AF21" s="123" t="s">
+      <c r="AC21" s="121"/>
+      <c r="AD21" s="121"/>
+      <c r="AE21" s="121"/>
+      <c r="AF21" s="121" t="s">
         <v>96</v>
       </c>
-      <c r="AG21" s="123"/>
-      <c r="AH21" s="123"/>
-      <c r="AI21" s="123"/>
+      <c r="AG21" s="121"/>
+      <c r="AH21" s="121"/>
+      <c r="AI21" s="121"/>
       <c r="AJ21" s="39" t="s">
         <v>60</v>
       </c>
@@ -3380,11 +3330,9 @@
       <c r="AS21" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="AU21" s="62"/>
-      <c r="AV21" s="62"/>
-      <c r="AW21" s="62"/>
-      <c r="AX21" s="62"/>
-      <c r="AY21" s="62"/>
+      <c r="AW21" s="35"/>
+      <c r="AX21" s="35"/>
+      <c r="AY21" s="35"/>
       <c r="AZ21" s="35"/>
       <c r="BA21" s="35"/>
       <c r="BB21" s="35"/>
@@ -3396,52 +3344,52 @@
       <c r="BH21" s="35"/>
     </row>
     <row r="22" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="78" t="s">
+      <c r="A22" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="88"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="90"/>
-      <c r="H22" s="91"/>
-      <c r="I22" s="74" t="s">
+      <c r="B22" s="90"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="J22" s="75"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="77" t="s">
+      <c r="J22" s="73"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="N22" s="75"/>
-      <c r="O22" s="76"/>
-      <c r="P22" s="76"/>
+      <c r="N22" s="73"/>
+      <c r="O22" s="74"/>
+      <c r="P22" s="74"/>
       <c r="Q22" s="6"/>
       <c r="R22" s="23"/>
-      <c r="S22" s="78" t="s">
+      <c r="S22" s="76" t="s">
         <v>111</v>
       </c>
-      <c r="T22" s="92"/>
-      <c r="U22" s="88"/>
-      <c r="V22" s="89"/>
-      <c r="W22" s="90"/>
-      <c r="X22" s="89"/>
-      <c r="Y22" s="90"/>
-      <c r="Z22" s="91"/>
-      <c r="AA22" s="74" t="s">
+      <c r="T22" s="90"/>
+      <c r="U22" s="86"/>
+      <c r="V22" s="87"/>
+      <c r="W22" s="88"/>
+      <c r="X22" s="87"/>
+      <c r="Y22" s="88"/>
+      <c r="Z22" s="89"/>
+      <c r="AA22" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="AB22" s="75"/>
-      <c r="AC22" s="76"/>
-      <c r="AD22" s="76"/>
-      <c r="AE22" s="77" t="s">
+      <c r="AB22" s="73"/>
+      <c r="AC22" s="74"/>
+      <c r="AD22" s="74"/>
+      <c r="AE22" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="AF22" s="75"/>
-      <c r="AG22" s="76"/>
-      <c r="AH22" s="76"/>
+      <c r="AF22" s="73"/>
+      <c r="AG22" s="74"/>
+      <c r="AH22" s="74"/>
       <c r="AI22" s="6"/>
       <c r="AJ22" s="40" t="s">
         <v>61</v>
@@ -3465,11 +3413,9 @@
         <v>80</v>
       </c>
       <c r="AS22" s="37"/>
-      <c r="AU22" s="62"/>
-      <c r="AV22" s="62"/>
-      <c r="AW22" s="62"/>
-      <c r="AX22" s="62"/>
-      <c r="AY22" s="62"/>
+      <c r="AW22" s="35"/>
+      <c r="AX22" s="35"/>
+      <c r="AY22" s="35"/>
       <c r="AZ22" s="35"/>
       <c r="BA22" s="35"/>
       <c r="BB22" s="35"/>
@@ -3481,35 +3427,35 @@
       <c r="BH22" s="35"/>
     </row>
     <row r="23" spans="1:60" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="69" t="s">
+      <c r="C23" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69" t="s">
+      <c r="D23" s="67"/>
+      <c r="E23" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69" t="s">
+      <c r="F23" s="67"/>
+      <c r="G23" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="69"/>
+      <c r="H23" s="67"/>
       <c r="L23" s="11"/>
       <c r="M23" s="5"/>
       <c r="N23" s="3"/>
       <c r="O23" s="22"/>
       <c r="R23" s="23"/>
-      <c r="U23" s="69" t="s">
+      <c r="U23" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="V23" s="69"/>
-      <c r="W23" s="69" t="s">
+      <c r="V23" s="67"/>
+      <c r="W23" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="X23" s="69"/>
-      <c r="Y23" s="69" t="s">
+      <c r="X23" s="67"/>
+      <c r="Y23" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="Z23" s="69"/>
+      <c r="Z23" s="67"/>
       <c r="AD23" s="11"/>
       <c r="AE23" s="5"/>
       <c r="AF23" s="3"/>
@@ -3539,11 +3485,9 @@
         <v>81</v>
       </c>
       <c r="AS23" s="38"/>
-      <c r="AU23" s="62"/>
-      <c r="AV23" s="62"/>
-      <c r="AW23" s="62"/>
-      <c r="AX23" s="62"/>
-      <c r="AY23" s="62"/>
+      <c r="AW23" s="35"/>
+      <c r="AX23" s="35"/>
+      <c r="AY23" s="35"/>
       <c r="AZ23" s="35"/>
       <c r="BA23" s="35"/>
       <c r="BB23" s="35"/>
@@ -3555,51 +3499,51 @@
       <c r="BH23" s="35"/>
     </row>
     <row r="24" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="78" t="s">
+      <c r="A24" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="88"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="74" t="s">
+      <c r="B24" s="90"/>
+      <c r="C24" s="86"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="J24" s="75"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="77" t="s">
+      <c r="J24" s="73"/>
+      <c r="K24" s="74"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="N24" s="75"/>
-      <c r="O24" s="76"/>
-      <c r="P24" s="76"/>
+      <c r="N24" s="73"/>
+      <c r="O24" s="74"/>
+      <c r="P24" s="74"/>
       <c r="R24" s="23"/>
-      <c r="S24" s="78" t="s">
+      <c r="S24" s="76" t="s">
         <v>112</v>
       </c>
-      <c r="T24" s="92"/>
-      <c r="U24" s="88"/>
-      <c r="V24" s="89"/>
-      <c r="W24" s="90"/>
-      <c r="X24" s="89"/>
-      <c r="Y24" s="90"/>
-      <c r="Z24" s="91"/>
-      <c r="AA24" s="74" t="s">
+      <c r="T24" s="90"/>
+      <c r="U24" s="86"/>
+      <c r="V24" s="87"/>
+      <c r="W24" s="88"/>
+      <c r="X24" s="87"/>
+      <c r="Y24" s="88"/>
+      <c r="Z24" s="89"/>
+      <c r="AA24" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="AB24" s="75"/>
-      <c r="AC24" s="76"/>
-      <c r="AD24" s="76"/>
-      <c r="AE24" s="77" t="s">
+      <c r="AB24" s="73"/>
+      <c r="AC24" s="74"/>
+      <c r="AD24" s="74"/>
+      <c r="AE24" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="AF24" s="75"/>
-      <c r="AG24" s="76"/>
-      <c r="AH24" s="76"/>
+      <c r="AF24" s="73"/>
+      <c r="AG24" s="74"/>
+      <c r="AH24" s="74"/>
       <c r="AJ24" s="40" t="s">
         <v>52</v>
       </c>
@@ -3622,11 +3566,9 @@
         <v>82</v>
       </c>
       <c r="AS24" s="38"/>
-      <c r="AU24" s="62"/>
-      <c r="AV24" s="62"/>
-      <c r="AW24" s="62"/>
-      <c r="AX24" s="62"/>
-      <c r="AY24" s="62"/>
+      <c r="AW24" s="35"/>
+      <c r="AX24" s="35"/>
+      <c r="AY24" s="35"/>
       <c r="AZ24" s="35"/>
       <c r="BA24" s="35"/>
       <c r="BB24" s="35"/>
@@ -3638,18 +3580,18 @@
       <c r="BH24" s="35"/>
     </row>
     <row r="25" spans="1:60" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69" t="s">
+      <c r="D25" s="67"/>
+      <c r="E25" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="69"/>
-      <c r="G25" s="69" t="s">
+      <c r="F25" s="67"/>
+      <c r="G25" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="69"/>
+      <c r="H25" s="67"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="11"/>
@@ -3657,18 +3599,18 @@
       <c r="N25" s="3"/>
       <c r="O25" s="22"/>
       <c r="R25" s="23"/>
-      <c r="U25" s="69" t="s">
+      <c r="U25" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="V25" s="69"/>
-      <c r="W25" s="69" t="s">
+      <c r="V25" s="67"/>
+      <c r="W25" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="X25" s="69"/>
-      <c r="Y25" s="69" t="s">
+      <c r="X25" s="67"/>
+      <c r="Y25" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="Z25" s="69"/>
+      <c r="Z25" s="67"/>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
       <c r="AD25" s="11"/>
@@ -3694,11 +3636,9 @@
         <v>83</v>
       </c>
       <c r="AS25" s="38"/>
-      <c r="AU25" s="62"/>
-      <c r="AV25" s="62"/>
-      <c r="AW25" s="62"/>
-      <c r="AX25" s="62"/>
-      <c r="AY25" s="62"/>
+      <c r="AW25" s="35"/>
+      <c r="AX25" s="35"/>
+      <c r="AY25" s="35"/>
       <c r="AZ25" s="35"/>
       <c r="BA25" s="35"/>
       <c r="BB25" s="35"/>
@@ -3710,51 +3650,51 @@
       <c r="BH25" s="35"/>
     </row>
     <row r="26" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="78" t="s">
+      <c r="A26" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="92"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="90"/>
-      <c r="H26" s="91"/>
-      <c r="I26" s="74" t="s">
+      <c r="B26" s="90"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="88"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="88"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="J26" s="75"/>
-      <c r="K26" s="76"/>
-      <c r="L26" s="76"/>
-      <c r="M26" s="77" t="s">
+      <c r="J26" s="73"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="N26" s="75"/>
-      <c r="O26" s="76"/>
-      <c r="P26" s="76"/>
+      <c r="N26" s="73"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="74"/>
       <c r="R26" s="23"/>
-      <c r="S26" s="78" t="s">
+      <c r="S26" s="76" t="s">
         <v>113</v>
       </c>
-      <c r="T26" s="92"/>
-      <c r="U26" s="88"/>
-      <c r="V26" s="89"/>
-      <c r="W26" s="90"/>
-      <c r="X26" s="89"/>
-      <c r="Y26" s="90"/>
-      <c r="Z26" s="91"/>
-      <c r="AA26" s="74" t="s">
+      <c r="T26" s="90"/>
+      <c r="U26" s="86"/>
+      <c r="V26" s="87"/>
+      <c r="W26" s="88"/>
+      <c r="X26" s="87"/>
+      <c r="Y26" s="88"/>
+      <c r="Z26" s="89"/>
+      <c r="AA26" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="AB26" s="75"/>
-      <c r="AC26" s="76"/>
-      <c r="AD26" s="76"/>
-      <c r="AE26" s="77" t="s">
+      <c r="AB26" s="73"/>
+      <c r="AC26" s="74"/>
+      <c r="AD26" s="74"/>
+      <c r="AE26" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="AF26" s="75"/>
-      <c r="AG26" s="76"/>
-      <c r="AH26" s="76"/>
+      <c r="AF26" s="73"/>
+      <c r="AG26" s="74"/>
+      <c r="AH26" s="74"/>
       <c r="AJ26" s="40" t="s">
         <v>55</v>
       </c>
@@ -3771,11 +3711,9 @@
         <v>84</v>
       </c>
       <c r="AS26" s="38"/>
-      <c r="AU26" s="62"/>
-      <c r="AV26" s="62"/>
-      <c r="AW26" s="62"/>
-      <c r="AX26" s="62"/>
-      <c r="AY26" s="62"/>
+      <c r="AW26" s="35"/>
+      <c r="AX26" s="35"/>
+      <c r="AY26" s="35"/>
       <c r="AZ26" s="35"/>
       <c r="BA26" s="35"/>
       <c r="BB26" s="35"/>
@@ -3787,18 +3725,18 @@
       <c r="BH26" s="35"/>
     </row>
     <row r="27" spans="1:60" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="69" t="s">
+      <c r="C27" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69" t="s">
+      <c r="D27" s="67"/>
+      <c r="E27" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69" t="s">
+      <c r="F27" s="67"/>
+      <c r="G27" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="H27" s="69"/>
+      <c r="H27" s="67"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="11"/>
@@ -3806,18 +3744,18 @@
       <c r="N27" s="3"/>
       <c r="O27" s="22"/>
       <c r="R27" s="23"/>
-      <c r="U27" s="69" t="s">
+      <c r="U27" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="V27" s="69"/>
-      <c r="W27" s="69" t="s">
+      <c r="V27" s="67"/>
+      <c r="W27" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="X27" s="69"/>
-      <c r="Y27" s="69" t="s">
+      <c r="X27" s="67"/>
+      <c r="Y27" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="Z27" s="69"/>
+      <c r="Z27" s="67"/>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
       <c r="AD27" s="11"/>
@@ -3840,11 +3778,9 @@
         <v>85</v>
       </c>
       <c r="AS27" s="38"/>
-      <c r="AU27" s="62"/>
-      <c r="AV27" s="62"/>
-      <c r="AW27" s="62"/>
-      <c r="AX27" s="62"/>
-      <c r="AY27" s="62"/>
+      <c r="AW27" s="35"/>
+      <c r="AX27" s="35"/>
+      <c r="AY27" s="35"/>
       <c r="AZ27" s="35"/>
       <c r="BA27" s="35"/>
       <c r="BB27" s="35"/>
@@ -3856,51 +3792,51 @@
       <c r="BH27" s="35"/>
     </row>
     <row r="28" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A28" s="78" t="s">
+      <c r="A28" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="92"/>
-      <c r="C28" s="88"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="90"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="90"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="74" t="s">
+      <c r="B28" s="90"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="87"/>
+      <c r="E28" s="88"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="88"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="J28" s="75"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="76"/>
-      <c r="M28" s="77" t="s">
+      <c r="J28" s="73"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="N28" s="75"/>
-      <c r="O28" s="76"/>
-      <c r="P28" s="76"/>
+      <c r="N28" s="73"/>
+      <c r="O28" s="74"/>
+      <c r="P28" s="74"/>
       <c r="R28" s="23"/>
-      <c r="S28" s="78" t="s">
+      <c r="S28" s="76" t="s">
         <v>114</v>
       </c>
-      <c r="T28" s="92"/>
-      <c r="U28" s="88"/>
-      <c r="V28" s="89"/>
-      <c r="W28" s="90"/>
-      <c r="X28" s="89"/>
-      <c r="Y28" s="90"/>
-      <c r="Z28" s="91"/>
-      <c r="AA28" s="74" t="s">
+      <c r="T28" s="90"/>
+      <c r="U28" s="86"/>
+      <c r="V28" s="87"/>
+      <c r="W28" s="88"/>
+      <c r="X28" s="87"/>
+      <c r="Y28" s="88"/>
+      <c r="Z28" s="89"/>
+      <c r="AA28" s="72" t="s">
         <v>97</v>
       </c>
-      <c r="AB28" s="75"/>
-      <c r="AC28" s="76"/>
-      <c r="AD28" s="76"/>
-      <c r="AE28" s="77" t="s">
+      <c r="AB28" s="73"/>
+      <c r="AC28" s="74"/>
+      <c r="AD28" s="74"/>
+      <c r="AE28" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="AF28" s="75"/>
-      <c r="AG28" s="76"/>
-      <c r="AH28" s="76"/>
+      <c r="AF28" s="73"/>
+      <c r="AG28" s="74"/>
+      <c r="AH28" s="74"/>
       <c r="AJ28" s="40" t="s">
         <v>56</v>
       </c>
@@ -3917,11 +3853,9 @@
         <v>86</v>
       </c>
       <c r="AS28" s="38"/>
-      <c r="AU28" s="62"/>
-      <c r="AV28" s="62"/>
-      <c r="AW28" s="62"/>
-      <c r="AX28" s="62"/>
-      <c r="AY28" s="62"/>
+      <c r="AW28" s="35"/>
+      <c r="AX28" s="35"/>
+      <c r="AY28" s="35"/>
       <c r="AZ28" s="35"/>
       <c r="BA28" s="35"/>
       <c r="BB28" s="35"/>
@@ -3933,18 +3867,18 @@
       <c r="BH28" s="35"/>
     </row>
     <row r="29" spans="1:60" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69" t="s">
+      <c r="D29" s="67"/>
+      <c r="E29" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="69"/>
-      <c r="G29" s="69" t="s">
+      <c r="F29" s="67"/>
+      <c r="G29" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="H29" s="69"/>
+      <c r="H29" s="67"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
@@ -3953,18 +3887,18 @@
       <c r="P29" s="24"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="23"/>
-      <c r="U29" s="69" t="s">
+      <c r="U29" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="V29" s="69"/>
-      <c r="W29" s="69" t="s">
+      <c r="V29" s="67"/>
+      <c r="W29" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="X29" s="69"/>
-      <c r="Y29" s="69" t="s">
+      <c r="X29" s="67"/>
+      <c r="Y29" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="Z29" s="69"/>
+      <c r="Z29" s="67"/>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
@@ -3988,11 +3922,9 @@
         <v>87</v>
       </c>
       <c r="AS29" s="38"/>
-      <c r="AU29" s="62"/>
-      <c r="AV29" s="62"/>
-      <c r="AW29" s="62"/>
-      <c r="AX29" s="62"/>
-      <c r="AY29" s="62"/>
+      <c r="AW29" s="35"/>
+      <c r="AX29" s="35"/>
+      <c r="AY29" s="35"/>
       <c r="AZ29" s="35"/>
       <c r="BA29" s="35"/>
       <c r="BB29" s="35"/>
@@ -4004,24 +3936,24 @@
       <c r="BH29" s="35"/>
     </row>
     <row r="30" spans="1:60" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="120"/>
-      <c r="C30" s="120"/>
-      <c r="D30" s="120"/>
-      <c r="E30" s="120"/>
-      <c r="F30" s="120"/>
-      <c r="G30" s="120"/>
-      <c r="H30" s="120"/>
-      <c r="I30" s="120"/>
-      <c r="J30" s="120"/>
-      <c r="K30" s="120"/>
-      <c r="L30" s="120"/>
-      <c r="M30" s="120"/>
-      <c r="N30" s="120"/>
-      <c r="O30" s="120"/>
-      <c r="P30" s="120"/>
-      <c r="R30" s="126"/>
-      <c r="S30" s="126"/>
-      <c r="T30" s="126"/>
+      <c r="B30" s="118"/>
+      <c r="C30" s="118"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="118"/>
+      <c r="G30" s="118"/>
+      <c r="H30" s="118"/>
+      <c r="I30" s="118"/>
+      <c r="J30" s="118"/>
+      <c r="K30" s="118"/>
+      <c r="L30" s="118"/>
+      <c r="M30" s="118"/>
+      <c r="N30" s="118"/>
+      <c r="O30" s="118"/>
+      <c r="P30" s="118"/>
+      <c r="R30" s="124"/>
+      <c r="S30" s="124"/>
+      <c r="T30" s="124"/>
       <c r="U30" s="23"/>
       <c r="V30" s="23"/>
       <c r="W30" s="23"/>
@@ -4053,11 +3985,9 @@
         <v>88</v>
       </c>
       <c r="AS30" s="38"/>
-      <c r="AU30" s="62"/>
-      <c r="AV30" s="62"/>
-      <c r="AW30" s="62"/>
-      <c r="AX30" s="62"/>
-      <c r="AY30" s="62"/>
+      <c r="AW30" s="35"/>
+      <c r="AX30" s="35"/>
+      <c r="AY30" s="35"/>
       <c r="AZ30" s="35"/>
       <c r="BA30" s="35"/>
       <c r="BB30" s="35"/>
@@ -4116,11 +4046,9 @@
         <v>151</v>
       </c>
       <c r="AS31" s="38"/>
-      <c r="AU31" s="62"/>
-      <c r="AV31" s="62"/>
-      <c r="AW31" s="62"/>
-      <c r="AX31" s="62"/>
-      <c r="AY31" s="62"/>
+      <c r="AW31" s="35"/>
+      <c r="AX31" s="35"/>
+      <c r="AY31" s="35"/>
       <c r="AZ31" s="35"/>
       <c r="BA31" s="35"/>
       <c r="BB31" s="35"/>
@@ -4135,24 +4063,24 @@
       <c r="A32" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="127" t="s">
+      <c r="B32" s="125" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="128"/>
-      <c r="D32" s="128"/>
-      <c r="E32" s="128"/>
-      <c r="F32" s="128"/>
-      <c r="G32" s="128"/>
-      <c r="H32" s="128"/>
-      <c r="I32" s="128"/>
-      <c r="J32" s="128"/>
-      <c r="K32" s="128"/>
-      <c r="L32" s="128"/>
-      <c r="M32" s="128"/>
-      <c r="N32" s="128"/>
-      <c r="O32" s="128"/>
-      <c r="P32" s="128"/>
-      <c r="Q32" s="128"/>
+      <c r="C32" s="126"/>
+      <c r="D32" s="126"/>
+      <c r="E32" s="126"/>
+      <c r="F32" s="126"/>
+      <c r="G32" s="126"/>
+      <c r="H32" s="126"/>
+      <c r="I32" s="126"/>
+      <c r="J32" s="126"/>
+      <c r="K32" s="126"/>
+      <c r="L32" s="126"/>
+      <c r="M32" s="126"/>
+      <c r="N32" s="126"/>
+      <c r="O32" s="126"/>
+      <c r="P32" s="126"/>
+      <c r="Q32" s="126"/>
       <c r="R32" s="4"/>
       <c r="S32" s="44"/>
       <c r="T32" s="44"/>
@@ -4183,11 +4111,9 @@
         <v>152</v>
       </c>
       <c r="AS32" s="38"/>
-      <c r="AU32" s="62"/>
-      <c r="AV32" s="62"/>
-      <c r="AW32" s="62"/>
-      <c r="AX32" s="62"/>
-      <c r="AY32" s="62"/>
+      <c r="AW32" s="35"/>
+      <c r="AX32" s="35"/>
+      <c r="AY32" s="35"/>
       <c r="AZ32" s="35"/>
       <c r="BA32" s="35"/>
       <c r="BB32" s="35"/>
@@ -4199,51 +4125,51 @@
       <c r="BH32" s="35"/>
     </row>
     <row r="33" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A33" s="78" t="s">
+      <c r="A33" s="76" t="s">
         <v>119</v>
       </c>
-      <c r="B33" s="78"/>
-      <c r="C33" s="163" t="s">
+      <c r="B33" s="76"/>
+      <c r="C33" s="161" t="s">
         <v>50</v>
       </c>
-      <c r="D33" s="163"/>
-      <c r="E33" s="163"/>
-      <c r="F33" s="163"/>
-      <c r="G33" s="163"/>
-      <c r="H33" s="163"/>
-      <c r="I33" s="163"/>
+      <c r="D33" s="161"/>
+      <c r="E33" s="161"/>
+      <c r="F33" s="161"/>
+      <c r="G33" s="161"/>
+      <c r="H33" s="161"/>
+      <c r="I33" s="161"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="124" t="s">
+      <c r="K33" s="122" t="s">
         <v>120</v>
       </c>
-      <c r="L33" s="125"/>
-      <c r="M33" s="125"/>
-      <c r="N33" s="125"/>
-      <c r="O33" s="125"/>
-      <c r="P33" s="125"/>
-      <c r="Q33" s="125"/>
-      <c r="R33" s="66"/>
-      <c r="S33" s="122" t="s">
+      <c r="L33" s="123"/>
+      <c r="M33" s="123"/>
+      <c r="N33" s="123"/>
+      <c r="O33" s="123"/>
+      <c r="P33" s="123"/>
+      <c r="Q33" s="123"/>
+      <c r="R33" s="64"/>
+      <c r="S33" s="120" t="s">
         <v>121</v>
       </c>
-      <c r="T33" s="122"/>
-      <c r="U33" s="122"/>
-      <c r="V33" s="122"/>
-      <c r="W33" s="122"/>
-      <c r="X33" s="122"/>
-      <c r="Y33" s="122"/>
-      <c r="Z33" s="122"/>
+      <c r="T33" s="120"/>
+      <c r="U33" s="120"/>
+      <c r="V33" s="120"/>
+      <c r="W33" s="120"/>
+      <c r="X33" s="120"/>
+      <c r="Y33" s="120"/>
+      <c r="Z33" s="120"/>
       <c r="AA33" s="4"/>
-      <c r="AB33" s="77" t="s">
+      <c r="AB33" s="75" t="s">
         <v>122</v>
       </c>
-      <c r="AC33" s="77"/>
-      <c r="AD33" s="77"/>
-      <c r="AE33" s="77"/>
-      <c r="AF33" s="77"/>
-      <c r="AG33" s="77"/>
-      <c r="AH33" s="77"/>
-      <c r="AI33" s="77"/>
+      <c r="AC33" s="75"/>
+      <c r="AD33" s="75"/>
+      <c r="AE33" s="75"/>
+      <c r="AF33" s="75"/>
+      <c r="AG33" s="75"/>
+      <c r="AH33" s="75"/>
+      <c r="AI33" s="75"/>
       <c r="AJ33" s="39"/>
       <c r="AO33" s="38" t="s">
         <v>132</v>
@@ -4256,11 +4182,9 @@
         <v>154</v>
       </c>
       <c r="AS33" s="38"/>
-      <c r="AU33" s="62"/>
-      <c r="AV33" s="62"/>
-      <c r="AW33" s="62"/>
-      <c r="AX33" s="62"/>
-      <c r="AY33" s="62"/>
+      <c r="AW33" s="35"/>
+      <c r="AX33" s="35"/>
+      <c r="AY33" s="35"/>
       <c r="AZ33" s="35"/>
       <c r="BA33" s="35"/>
       <c r="BB33" s="35"/>
@@ -4272,41 +4196,41 @@
       <c r="BH33" s="35"/>
     </row>
     <row r="34" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A34" s="78"/>
-      <c r="B34" s="78"/>
-      <c r="C34" s="164"/>
-      <c r="D34" s="165"/>
-      <c r="E34" s="165"/>
-      <c r="F34" s="165"/>
-      <c r="G34" s="165"/>
-      <c r="H34" s="165"/>
-      <c r="I34" s="166"/>
+      <c r="A34" s="76"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="162"/>
+      <c r="D34" s="163"/>
+      <c r="E34" s="163"/>
+      <c r="F34" s="163"/>
+      <c r="G34" s="163"/>
+      <c r="H34" s="163"/>
+      <c r="I34" s="164"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="79"/>
-      <c r="L34" s="80"/>
-      <c r="M34" s="80"/>
-      <c r="N34" s="80"/>
-      <c r="O34" s="80"/>
-      <c r="P34" s="80"/>
-      <c r="Q34" s="81"/>
+      <c r="K34" s="77"/>
+      <c r="L34" s="78"/>
+      <c r="M34" s="78"/>
+      <c r="N34" s="78"/>
+      <c r="O34" s="78"/>
+      <c r="P34" s="78"/>
+      <c r="Q34" s="79"/>
       <c r="R34" s="4"/>
-      <c r="S34" s="82"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="83"/>
-      <c r="V34" s="83"/>
-      <c r="W34" s="83"/>
-      <c r="X34" s="83"/>
-      <c r="Y34" s="83"/>
-      <c r="Z34" s="84"/>
+      <c r="S34" s="80"/>
+      <c r="T34" s="81"/>
+      <c r="U34" s="81"/>
+      <c r="V34" s="81"/>
+      <c r="W34" s="81"/>
+      <c r="X34" s="81"/>
+      <c r="Y34" s="81"/>
+      <c r="Z34" s="82"/>
       <c r="AA34" s="4"/>
-      <c r="AB34" s="156"/>
-      <c r="AC34" s="157"/>
-      <c r="AD34" s="157"/>
-      <c r="AE34" s="157"/>
-      <c r="AF34" s="157"/>
-      <c r="AG34" s="157"/>
-      <c r="AH34" s="157"/>
-      <c r="AI34" s="158"/>
+      <c r="AB34" s="154"/>
+      <c r="AC34" s="155"/>
+      <c r="AD34" s="155"/>
+      <c r="AE34" s="155"/>
+      <c r="AF34" s="155"/>
+      <c r="AG34" s="155"/>
+      <c r="AH34" s="155"/>
+      <c r="AI34" s="156"/>
       <c r="AJ34" s="39"/>
       <c r="AO34" s="38" t="s">
         <v>133</v>
@@ -4319,11 +4243,9 @@
         <v>89</v>
       </c>
       <c r="AS34" s="38"/>
-      <c r="AU34" s="62"/>
-      <c r="AV34" s="62"/>
-      <c r="AW34" s="62"/>
-      <c r="AX34" s="62"/>
-      <c r="AY34" s="62"/>
+      <c r="AW34" s="35"/>
+      <c r="AX34" s="35"/>
+      <c r="AY34" s="35"/>
       <c r="AZ34" s="35"/>
       <c r="BA34" s="35"/>
       <c r="BB34" s="35"/>
@@ -4337,47 +4259,47 @@
     <row r="35" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
-      <c r="C35" s="154" t="s">
+      <c r="C35" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="154"/>
-      <c r="E35" s="154"/>
-      <c r="F35" s="154"/>
-      <c r="G35" s="154"/>
-      <c r="H35" s="154"/>
-      <c r="I35" s="154"/>
+      <c r="D35" s="152"/>
+      <c r="E35" s="152"/>
+      <c r="F35" s="152"/>
+      <c r="G35" s="152"/>
+      <c r="H35" s="152"/>
+      <c r="I35" s="152"/>
       <c r="J35" s="13"/>
-      <c r="K35" s="155" t="s">
+      <c r="K35" s="153" t="s">
         <v>51</v>
       </c>
-      <c r="L35" s="155"/>
-      <c r="M35" s="155"/>
-      <c r="N35" s="155"/>
-      <c r="O35" s="155"/>
-      <c r="P35" s="155"/>
-      <c r="Q35" s="155"/>
+      <c r="L35" s="153"/>
+      <c r="M35" s="153"/>
+      <c r="N35" s="153"/>
+      <c r="O35" s="153"/>
+      <c r="P35" s="153"/>
+      <c r="Q35" s="153"/>
       <c r="R35" s="4"/>
-      <c r="S35" s="87" t="s">
+      <c r="S35" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="T35" s="87"/>
-      <c r="U35" s="70"/>
-      <c r="V35" s="71"/>
-      <c r="W35" s="72" t="s">
+      <c r="T35" s="85"/>
+      <c r="U35" s="68"/>
+      <c r="V35" s="69"/>
+      <c r="W35" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="X35" s="73"/>
-      <c r="Y35" s="70"/>
-      <c r="Z35" s="71"/>
+      <c r="X35" s="71"/>
+      <c r="Y35" s="68"/>
+      <c r="Z35" s="69"/>
       <c r="AA35" s="4"/>
-      <c r="AB35" s="159"/>
-      <c r="AC35" s="160"/>
-      <c r="AD35" s="160"/>
-      <c r="AE35" s="160"/>
-      <c r="AF35" s="160"/>
-      <c r="AG35" s="160"/>
-      <c r="AH35" s="160"/>
-      <c r="AI35" s="161"/>
+      <c r="AB35" s="157"/>
+      <c r="AC35" s="158"/>
+      <c r="AD35" s="158"/>
+      <c r="AE35" s="158"/>
+      <c r="AF35" s="158"/>
+      <c r="AG35" s="158"/>
+      <c r="AH35" s="158"/>
+      <c r="AI35" s="159"/>
       <c r="AJ35" s="39"/>
       <c r="AO35" s="38" t="s">
         <v>156</v>
@@ -4390,11 +4312,9 @@
         <v>90</v>
       </c>
       <c r="AS35" s="38"/>
-      <c r="AU35" s="62"/>
-      <c r="AV35" s="62"/>
-      <c r="AW35" s="62"/>
-      <c r="AX35" s="62"/>
-      <c r="AY35" s="62"/>
+      <c r="AW35" s="35"/>
+      <c r="AX35" s="35"/>
+      <c r="AY35" s="35"/>
       <c r="AZ35" s="35"/>
       <c r="BA35" s="35"/>
       <c r="BB35" s="35"/>
@@ -4415,24 +4335,24 @@
       <c r="H36" s="49"/>
       <c r="I36" s="49"/>
       <c r="J36" s="49"/>
-      <c r="K36" s="98"/>
-      <c r="L36" s="98"/>
-      <c r="M36" s="98"/>
-      <c r="N36" s="98"/>
-      <c r="O36" s="98"/>
-      <c r="P36" s="98"/>
-      <c r="Q36" s="98"/>
+      <c r="K36" s="96"/>
+      <c r="L36" s="96"/>
+      <c r="M36" s="96"/>
+      <c r="N36" s="96"/>
+      <c r="O36" s="96"/>
+      <c r="P36" s="96"/>
+      <c r="Q36" s="96"/>
       <c r="R36" s="4"/>
-      <c r="S36" s="85" t="s">
+      <c r="S36" s="83" t="s">
         <v>118</v>
       </c>
-      <c r="T36" s="86"/>
-      <c r="U36" s="86"/>
-      <c r="V36" s="86"/>
-      <c r="W36" s="86"/>
-      <c r="X36" s="86"/>
-      <c r="Y36" s="86"/>
-      <c r="Z36" s="86"/>
+      <c r="T36" s="84"/>
+      <c r="U36" s="84"/>
+      <c r="V36" s="84"/>
+      <c r="W36" s="84"/>
+      <c r="X36" s="84"/>
+      <c r="Y36" s="84"/>
+      <c r="Z36" s="84"/>
       <c r="AA36" s="4"/>
       <c r="AB36" s="44"/>
       <c r="AC36" s="44"/>
@@ -4454,11 +4374,9 @@
         <v>91</v>
       </c>
       <c r="AS36" s="38"/>
-      <c r="AU36" s="62"/>
-      <c r="AV36" s="62"/>
-      <c r="AW36" s="62"/>
-      <c r="AX36" s="62"/>
-      <c r="AY36" s="62"/>
+      <c r="AW36" s="35"/>
+      <c r="AX36" s="35"/>
+      <c r="AY36" s="35"/>
       <c r="AZ36" s="35"/>
       <c r="BA36" s="35"/>
       <c r="BB36" s="35"/>
@@ -4470,47 +4388,47 @@
       <c r="BH36" s="35"/>
     </row>
     <row r="37" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A37" s="63" t="s">
+      <c r="A37" s="61" t="s">
         <v>123</v>
       </c>
-      <c r="B37" s="64"/>
-      <c r="C37" s="65" t="s">
+      <c r="B37" s="62"/>
+      <c r="C37" s="63" t="s">
         <v>128</v>
       </c>
-      <c r="D37" s="66"/>
-      <c r="E37" s="66"/>
-      <c r="F37" s="66"/>
-      <c r="G37" s="66"/>
-      <c r="H37" s="66"/>
-      <c r="I37" s="66"/>
-      <c r="J37" s="66"/>
-      <c r="K37" s="66"/>
-      <c r="L37" s="66"/>
-      <c r="M37" s="66"/>
-      <c r="N37" s="66"/>
-      <c r="O37" s="136" t="s">
+      <c r="D37" s="64"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="64"/>
+      <c r="J37" s="64"/>
+      <c r="K37" s="64"/>
+      <c r="L37" s="64"/>
+      <c r="M37" s="64"/>
+      <c r="N37" s="64"/>
+      <c r="O37" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="P37" s="137"/>
-      <c r="Q37" s="138"/>
+      <c r="P37" s="135"/>
+      <c r="Q37" s="136"/>
       <c r="R37" s="53"/>
-      <c r="S37" s="76"/>
-      <c r="T37" s="76"/>
-      <c r="U37" s="76"/>
-      <c r="V37" s="76"/>
-      <c r="W37" s="76"/>
-      <c r="X37" s="76"/>
-      <c r="Y37" s="76"/>
-      <c r="Z37" s="76"/>
+      <c r="S37" s="74"/>
+      <c r="T37" s="74"/>
+      <c r="U37" s="74"/>
+      <c r="V37" s="74"/>
+      <c r="W37" s="74"/>
+      <c r="X37" s="74"/>
+      <c r="Y37" s="74"/>
+      <c r="Z37" s="74"/>
       <c r="AA37" s="4"/>
-      <c r="AB37" s="77"/>
-      <c r="AC37" s="77"/>
-      <c r="AD37" s="77"/>
-      <c r="AE37" s="77"/>
-      <c r="AF37" s="77"/>
-      <c r="AG37" s="77"/>
-      <c r="AH37" s="77"/>
-      <c r="AI37" s="77"/>
+      <c r="AB37" s="75"/>
+      <c r="AC37" s="75"/>
+      <c r="AD37" s="75"/>
+      <c r="AE37" s="75"/>
+      <c r="AF37" s="75"/>
+      <c r="AG37" s="75"/>
+      <c r="AH37" s="75"/>
+      <c r="AI37" s="75"/>
       <c r="AJ37" s="39"/>
       <c r="AO37" s="38" t="s">
         <v>135</v>
@@ -4523,11 +4441,9 @@
         <v>92</v>
       </c>
       <c r="AS37" s="38"/>
-      <c r="AU37" s="62"/>
-      <c r="AV37" s="62"/>
-      <c r="AW37" s="62"/>
-      <c r="AX37" s="62"/>
-      <c r="AY37" s="62"/>
+      <c r="AW37" s="35"/>
+      <c r="AX37" s="35"/>
+      <c r="AY37" s="35"/>
       <c r="AZ37" s="35"/>
       <c r="BA37" s="35"/>
       <c r="BB37" s="35"/>
@@ -4541,18 +4457,18 @@
     <row r="38" spans="1:60" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="43"/>
       <c r="B38" s="54"/>
-      <c r="C38" s="66"/>
-      <c r="D38" s="66"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="66"/>
-      <c r="J38" s="66"/>
-      <c r="K38" s="66"/>
-      <c r="L38" s="66"/>
-      <c r="M38" s="66"/>
-      <c r="N38" s="66"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="64"/>
+      <c r="K38" s="64"/>
+      <c r="L38" s="64"/>
+      <c r="M38" s="64"/>
+      <c r="N38" s="64"/>
       <c r="O38" s="46"/>
       <c r="P38" s="46"/>
       <c r="Q38" s="46"/>
@@ -4586,11 +4502,9 @@
         <v>153</v>
       </c>
       <c r="AS38" s="38"/>
-      <c r="AU38" s="62"/>
-      <c r="AV38" s="62"/>
-      <c r="AW38" s="62"/>
-      <c r="AX38" s="62"/>
-      <c r="AY38" s="62"/>
+      <c r="AW38" s="35"/>
+      <c r="AX38" s="35"/>
+      <c r="AY38" s="35"/>
       <c r="AZ38" s="35"/>
       <c r="BA38" s="35"/>
       <c r="BB38" s="35"/>
@@ -4602,31 +4516,31 @@
       <c r="BH38" s="35"/>
     </row>
     <row r="39" spans="1:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C39" s="162"/>
-      <c r="D39" s="162"/>
-      <c r="E39" s="162"/>
-      <c r="F39" s="162"/>
-      <c r="G39" s="162"/>
-      <c r="H39" s="162"/>
-      <c r="I39" s="162"/>
+      <c r="C39" s="160"/>
+      <c r="D39" s="160"/>
+      <c r="E39" s="160"/>
+      <c r="F39" s="160"/>
+      <c r="G39" s="160"/>
+      <c r="H39" s="160"/>
+      <c r="I39" s="160"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="98"/>
-      <c r="L39" s="98"/>
-      <c r="M39" s="98"/>
-      <c r="N39" s="98"/>
-      <c r="O39" s="98"/>
-      <c r="P39" s="98"/>
-      <c r="Q39" s="98"/>
-      <c r="S39" s="85" t="s">
+      <c r="K39" s="96"/>
+      <c r="L39" s="96"/>
+      <c r="M39" s="96"/>
+      <c r="N39" s="96"/>
+      <c r="O39" s="96"/>
+      <c r="P39" s="96"/>
+      <c r="Q39" s="96"/>
+      <c r="S39" s="83" t="s">
         <v>167</v>
       </c>
-      <c r="T39" s="86"/>
-      <c r="U39" s="86"/>
-      <c r="V39" s="86"/>
-      <c r="W39" s="86"/>
-      <c r="X39" s="86"/>
-      <c r="Y39" s="86"/>
-      <c r="Z39" s="86"/>
+      <c r="T39" s="84"/>
+      <c r="U39" s="84"/>
+      <c r="V39" s="84"/>
+      <c r="W39" s="84"/>
+      <c r="X39" s="84"/>
+      <c r="Y39" s="84"/>
+      <c r="Z39" s="84"/>
       <c r="AB39" s="44"/>
       <c r="AC39" s="44"/>
       <c r="AD39" s="44"/>
@@ -4647,11 +4561,9 @@
         <v>155</v>
       </c>
       <c r="AS39" s="38"/>
-      <c r="AU39" s="62"/>
-      <c r="AV39" s="62"/>
-      <c r="AW39" s="62"/>
-      <c r="AX39" s="62"/>
-      <c r="AY39" s="62"/>
+      <c r="AW39" s="35"/>
+      <c r="AX39" s="35"/>
+      <c r="AY39" s="35"/>
       <c r="AZ39" s="35"/>
       <c r="BA39" s="35"/>
       <c r="BB39" s="35"/>
@@ -4663,45 +4575,45 @@
       <c r="BH39" s="35"/>
     </row>
     <row r="40" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="63" t="s">
+      <c r="A40" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="67" t="s">
+      <c r="B40" s="62"/>
+      <c r="C40" s="65" t="s">
         <v>129</v>
       </c>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="68"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="68"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
+      <c r="H40" s="66"/>
+      <c r="I40" s="66"/>
+      <c r="J40" s="66"/>
+      <c r="K40" s="66"/>
+      <c r="L40" s="66"/>
+      <c r="M40" s="66"/>
       <c r="N40" s="55"/>
-      <c r="O40" s="136" t="s">
+      <c r="O40" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="P40" s="137"/>
-      <c r="Q40" s="138"/>
-      <c r="S40" s="88"/>
-      <c r="T40" s="91"/>
-      <c r="U40" s="90"/>
-      <c r="V40" s="91"/>
-      <c r="W40" s="90"/>
-      <c r="X40" s="91"/>
-      <c r="Y40" s="90"/>
-      <c r="Z40" s="91"/>
-      <c r="AB40" s="69"/>
-      <c r="AC40" s="69"/>
-      <c r="AD40" s="69"/>
-      <c r="AE40" s="69"/>
-      <c r="AF40" s="69"/>
-      <c r="AG40" s="69"/>
-      <c r="AH40" s="69"/>
-      <c r="AI40" s="69"/>
+      <c r="P40" s="135"/>
+      <c r="Q40" s="136"/>
+      <c r="S40" s="86"/>
+      <c r="T40" s="89"/>
+      <c r="U40" s="88"/>
+      <c r="V40" s="89"/>
+      <c r="W40" s="88"/>
+      <c r="X40" s="89"/>
+      <c r="Y40" s="88"/>
+      <c r="Z40" s="89"/>
+      <c r="AB40" s="67"/>
+      <c r="AC40" s="67"/>
+      <c r="AD40" s="67"/>
+      <c r="AE40" s="67"/>
+      <c r="AF40" s="67"/>
+      <c r="AG40" s="67"/>
+      <c r="AH40" s="67"/>
+      <c r="AI40" s="67"/>
       <c r="AJ40" s="39"/>
       <c r="AO40" s="38" t="s">
         <v>157</v>
@@ -4714,11 +4626,9 @@
         <v>93</v>
       </c>
       <c r="AS40" s="38"/>
-      <c r="AU40" s="62"/>
-      <c r="AV40" s="62"/>
-      <c r="AW40" s="62"/>
-      <c r="AX40" s="62"/>
-      <c r="AY40" s="62"/>
+      <c r="AW40" s="35"/>
+      <c r="AX40" s="35"/>
+      <c r="AY40" s="35"/>
       <c r="AZ40" s="35"/>
       <c r="BA40" s="35"/>
       <c r="BB40" s="35"/>
@@ -4777,11 +4687,9 @@
         <v>94</v>
       </c>
       <c r="AS41" s="38"/>
-      <c r="AU41" s="62"/>
-      <c r="AV41" s="62"/>
-      <c r="AW41" s="62"/>
-      <c r="AX41" s="62"/>
-      <c r="AY41" s="62"/>
+      <c r="AW41" s="35"/>
+      <c r="AX41" s="35"/>
+      <c r="AY41" s="35"/>
       <c r="AZ41" s="35"/>
       <c r="BA41" s="35"/>
       <c r="BB41" s="35"/>
@@ -4796,23 +4704,23 @@
       <c r="A42" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B42" s="120" t="s">
+      <c r="B42" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="120"/>
-      <c r="D42" s="120"/>
-      <c r="E42" s="120"/>
-      <c r="F42" s="120"/>
-      <c r="G42" s="120"/>
-      <c r="H42" s="120"/>
-      <c r="I42" s="120"/>
-      <c r="J42" s="120"/>
-      <c r="K42" s="120"/>
-      <c r="L42" s="120"/>
-      <c r="M42" s="120"/>
-      <c r="N42" s="120"/>
-      <c r="O42" s="120"/>
-      <c r="P42" s="120"/>
+      <c r="C42" s="118"/>
+      <c r="D42" s="118"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="118"/>
+      <c r="G42" s="118"/>
+      <c r="H42" s="118"/>
+      <c r="I42" s="118"/>
+      <c r="J42" s="118"/>
+      <c r="K42" s="118"/>
+      <c r="L42" s="118"/>
+      <c r="M42" s="118"/>
+      <c r="N42" s="118"/>
+      <c r="O42" s="118"/>
+      <c r="P42" s="118"/>
       <c r="AJ42" s="39"/>
       <c r="AO42" s="38" t="s">
         <v>159</v>
@@ -4825,11 +4733,9 @@
         <v>95</v>
       </c>
       <c r="AS42" s="38"/>
-      <c r="AU42" s="62"/>
-      <c r="AV42" s="62"/>
-      <c r="AW42" s="62"/>
-      <c r="AX42" s="62"/>
-      <c r="AY42" s="62"/>
+      <c r="AW42" s="35"/>
+      <c r="AX42" s="35"/>
+      <c r="AY42" s="35"/>
       <c r="AZ42" s="35"/>
       <c r="BA42" s="35"/>
       <c r="BB42" s="35"/>
@@ -4841,38 +4747,38 @@
       <c r="BH42" s="35"/>
     </row>
     <row r="43" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B43" s="105"/>
-      <c r="C43" s="106"/>
-      <c r="D43" s="106"/>
-      <c r="E43" s="106"/>
-      <c r="F43" s="106"/>
-      <c r="G43" s="106"/>
-      <c r="H43" s="106"/>
-      <c r="I43" s="106"/>
-      <c r="J43" s="106"/>
-      <c r="K43" s="106"/>
-      <c r="L43" s="106"/>
-      <c r="M43" s="106"/>
-      <c r="N43" s="106"/>
-      <c r="O43" s="107"/>
-      <c r="Q43" s="111"/>
-      <c r="R43" s="112"/>
-      <c r="S43" s="112"/>
-      <c r="T43" s="112"/>
-      <c r="U43" s="112"/>
-      <c r="V43" s="112"/>
-      <c r="W43" s="112"/>
-      <c r="X43" s="113"/>
-      <c r="Z43" s="105"/>
-      <c r="AA43" s="106"/>
-      <c r="AB43" s="106"/>
-      <c r="AC43" s="106"/>
-      <c r="AD43" s="106"/>
-      <c r="AE43" s="106"/>
-      <c r="AF43" s="106"/>
-      <c r="AG43" s="106"/>
-      <c r="AH43" s="106"/>
-      <c r="AI43" s="107"/>
+      <c r="B43" s="103"/>
+      <c r="C43" s="104"/>
+      <c r="D43" s="104"/>
+      <c r="E43" s="104"/>
+      <c r="F43" s="104"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="104"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="104"/>
+      <c r="K43" s="104"/>
+      <c r="L43" s="104"/>
+      <c r="M43" s="104"/>
+      <c r="N43" s="104"/>
+      <c r="O43" s="105"/>
+      <c r="Q43" s="109"/>
+      <c r="R43" s="110"/>
+      <c r="S43" s="110"/>
+      <c r="T43" s="110"/>
+      <c r="U43" s="110"/>
+      <c r="V43" s="110"/>
+      <c r="W43" s="110"/>
+      <c r="X43" s="111"/>
+      <c r="Z43" s="103"/>
+      <c r="AA43" s="104"/>
+      <c r="AB43" s="104"/>
+      <c r="AC43" s="104"/>
+      <c r="AD43" s="104"/>
+      <c r="AE43" s="104"/>
+      <c r="AF43" s="104"/>
+      <c r="AG43" s="104"/>
+      <c r="AH43" s="104"/>
+      <c r="AI43" s="105"/>
       <c r="AJ43" s="39"/>
       <c r="AO43" s="38" t="s">
         <v>160</v>
@@ -4883,11 +4789,9 @@
       </c>
       <c r="AR43" s="38"/>
       <c r="AS43" s="38"/>
-      <c r="AU43" s="62"/>
-      <c r="AV43" s="62"/>
-      <c r="AW43" s="62"/>
-      <c r="AX43" s="62"/>
-      <c r="AY43" s="62"/>
+      <c r="AW43" s="35"/>
+      <c r="AX43" s="35"/>
+      <c r="AY43" s="35"/>
       <c r="AZ43" s="35"/>
       <c r="BA43" s="35"/>
       <c r="BB43" s="35"/>
@@ -4899,38 +4803,38 @@
       <c r="BH43" s="35"/>
     </row>
     <row r="44" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B44" s="108"/>
-      <c r="C44" s="109"/>
-      <c r="D44" s="109"/>
-      <c r="E44" s="109"/>
-      <c r="F44" s="109"/>
-      <c r="G44" s="109"/>
-      <c r="H44" s="109"/>
-      <c r="I44" s="109"/>
-      <c r="J44" s="109"/>
-      <c r="K44" s="109"/>
-      <c r="L44" s="109"/>
-      <c r="M44" s="109"/>
-      <c r="N44" s="109"/>
-      <c r="O44" s="110"/>
-      <c r="Q44" s="114"/>
-      <c r="R44" s="115"/>
-      <c r="S44" s="115"/>
-      <c r="T44" s="115"/>
-      <c r="U44" s="115"/>
-      <c r="V44" s="115"/>
-      <c r="W44" s="115"/>
-      <c r="X44" s="116"/>
-      <c r="Z44" s="108"/>
-      <c r="AA44" s="109"/>
-      <c r="AB44" s="109"/>
-      <c r="AC44" s="109"/>
-      <c r="AD44" s="109"/>
-      <c r="AE44" s="109"/>
-      <c r="AF44" s="109"/>
-      <c r="AG44" s="109"/>
-      <c r="AH44" s="109"/>
-      <c r="AI44" s="110"/>
+      <c r="B44" s="106"/>
+      <c r="C44" s="107"/>
+      <c r="D44" s="107"/>
+      <c r="E44" s="107"/>
+      <c r="F44" s="107"/>
+      <c r="G44" s="107"/>
+      <c r="H44" s="107"/>
+      <c r="I44" s="107"/>
+      <c r="J44" s="107"/>
+      <c r="K44" s="107"/>
+      <c r="L44" s="107"/>
+      <c r="M44" s="107"/>
+      <c r="N44" s="107"/>
+      <c r="O44" s="108"/>
+      <c r="Q44" s="112"/>
+      <c r="R44" s="113"/>
+      <c r="S44" s="113"/>
+      <c r="T44" s="113"/>
+      <c r="U44" s="113"/>
+      <c r="V44" s="113"/>
+      <c r="W44" s="113"/>
+      <c r="X44" s="114"/>
+      <c r="Z44" s="106"/>
+      <c r="AA44" s="107"/>
+      <c r="AB44" s="107"/>
+      <c r="AC44" s="107"/>
+      <c r="AD44" s="107"/>
+      <c r="AE44" s="107"/>
+      <c r="AF44" s="107"/>
+      <c r="AG44" s="107"/>
+      <c r="AH44" s="107"/>
+      <c r="AI44" s="108"/>
       <c r="AJ44" s="39"/>
       <c r="AO44" s="38" t="s">
         <v>161</v>
@@ -4940,49 +4844,44 @@
       </c>
       <c r="AR44" s="38"/>
       <c r="AS44" s="38"/>
-      <c r="AU44" s="62"/>
-      <c r="AV44" s="62"/>
-      <c r="AW44" s="62"/>
-      <c r="AX44" s="62"/>
-      <c r="AY44" s="62"/>
     </row>
     <row r="45" spans="1:60" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="97" t="s">
+      <c r="B45" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="97"/>
-      <c r="D45" s="97"/>
-      <c r="E45" s="97"/>
-      <c r="F45" s="97"/>
-      <c r="G45" s="97"/>
-      <c r="H45" s="97"/>
-      <c r="I45" s="97"/>
-      <c r="J45" s="97"/>
-      <c r="K45" s="97"/>
-      <c r="L45" s="97"/>
-      <c r="M45" s="97"/>
-      <c r="N45" s="97"/>
-      <c r="O45" s="97"/>
-      <c r="Q45" s="117"/>
-      <c r="R45" s="118"/>
-      <c r="S45" s="118"/>
-      <c r="T45" s="118"/>
-      <c r="U45" s="118"/>
-      <c r="V45" s="118"/>
-      <c r="W45" s="118"/>
-      <c r="X45" s="119"/>
-      <c r="Z45" s="69" t="s">
+      <c r="C45" s="95"/>
+      <c r="D45" s="95"/>
+      <c r="E45" s="95"/>
+      <c r="F45" s="95"/>
+      <c r="G45" s="95"/>
+      <c r="H45" s="95"/>
+      <c r="I45" s="95"/>
+      <c r="J45" s="95"/>
+      <c r="K45" s="95"/>
+      <c r="L45" s="95"/>
+      <c r="M45" s="95"/>
+      <c r="N45" s="95"/>
+      <c r="O45" s="95"/>
+      <c r="Q45" s="115"/>
+      <c r="R45" s="116"/>
+      <c r="S45" s="116"/>
+      <c r="T45" s="116"/>
+      <c r="U45" s="116"/>
+      <c r="V45" s="116"/>
+      <c r="W45" s="116"/>
+      <c r="X45" s="117"/>
+      <c r="Z45" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="AA45" s="69"/>
-      <c r="AB45" s="69"/>
-      <c r="AC45" s="69"/>
-      <c r="AD45" s="69"/>
-      <c r="AE45" s="69"/>
-      <c r="AF45" s="69"/>
-      <c r="AG45" s="69"/>
-      <c r="AH45" s="69"/>
-      <c r="AI45" s="69"/>
+      <c r="AA45" s="67"/>
+      <c r="AB45" s="67"/>
+      <c r="AC45" s="67"/>
+      <c r="AD45" s="67"/>
+      <c r="AE45" s="67"/>
+      <c r="AF45" s="67"/>
+      <c r="AG45" s="67"/>
+      <c r="AH45" s="67"/>
+      <c r="AI45" s="67"/>
       <c r="AJ45" s="39"/>
       <c r="AO45" s="38" t="s">
         <v>162</v>
@@ -4993,26 +4892,21 @@
       </c>
       <c r="AR45" s="38"/>
       <c r="AS45" s="38"/>
-      <c r="AU45" s="62"/>
-      <c r="AV45" s="62"/>
-      <c r="AW45" s="62"/>
-      <c r="AX45" s="62"/>
-      <c r="AY45" s="62"/>
     </row>
     <row r="46" spans="1:60" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="O46" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="Q46" s="121" t="s">
+      <c r="Q46" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="R46" s="121"/>
-      <c r="S46" s="121"/>
-      <c r="T46" s="121"/>
-      <c r="U46" s="121"/>
-      <c r="V46" s="121"/>
-      <c r="W46" s="121"/>
-      <c r="X46" s="121"/>
+      <c r="R46" s="119"/>
+      <c r="S46" s="119"/>
+      <c r="T46" s="119"/>
+      <c r="U46" s="119"/>
+      <c r="V46" s="119"/>
+      <c r="W46" s="119"/>
+      <c r="X46" s="119"/>
       <c r="AJ46" s="39"/>
       <c r="AO46" s="38" t="s">
         <v>163</v>
@@ -5023,11 +4917,6 @@
       </c>
       <c r="AR46" s="38"/>
       <c r="AS46" s="38"/>
-      <c r="AU46" s="62"/>
-      <c r="AV46" s="62"/>
-      <c r="AW46" s="62"/>
-      <c r="AX46" s="62"/>
-      <c r="AY46" s="62"/>
     </row>
     <row r="47" spans="1:60" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="30" t="s">
@@ -5051,27 +4940,27 @@
       <c r="P47" s="28"/>
       <c r="Q47" s="28"/>
       <c r="R47" s="28"/>
-      <c r="S47" s="100"/>
-      <c r="T47" s="101"/>
-      <c r="U47" s="101"/>
-      <c r="V47" s="102"/>
+      <c r="S47" s="98"/>
+      <c r="T47" s="99"/>
+      <c r="U47" s="99"/>
+      <c r="V47" s="100"/>
       <c r="W47" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="X47" s="103"/>
-      <c r="Y47" s="100"/>
-      <c r="Z47" s="171"/>
-      <c r="AA47" s="172"/>
-      <c r="AB47" s="102"/>
-      <c r="AC47" s="103"/>
+      <c r="X47" s="101"/>
+      <c r="Y47" s="98"/>
+      <c r="Z47" s="169"/>
+      <c r="AA47" s="170"/>
+      <c r="AB47" s="100"/>
+      <c r="AC47" s="101"/>
       <c r="AD47" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="AE47" s="168"/>
-      <c r="AF47" s="169"/>
-      <c r="AG47" s="169"/>
-      <c r="AH47" s="169"/>
-      <c r="AI47" s="170"/>
+      <c r="AE47" s="166"/>
+      <c r="AF47" s="167"/>
+      <c r="AG47" s="167"/>
+      <c r="AH47" s="167"/>
+      <c r="AI47" s="168"/>
       <c r="AJ47" s="39"/>
       <c r="AO47" s="38" t="s">
         <v>164</v>
@@ -5082,38 +4971,33 @@
       </c>
       <c r="AR47" s="38"/>
       <c r="AS47" s="38"/>
-      <c r="AU47" s="62"/>
-      <c r="AV47" s="62"/>
-      <c r="AW47" s="62"/>
-      <c r="AX47" s="62"/>
-      <c r="AY47" s="62"/>
     </row>
     <row r="48" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="S48" s="99" t="s">
+      <c r="S48" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="T48" s="99"/>
-      <c r="U48" s="99"/>
-      <c r="V48" s="99"/>
-      <c r="X48" s="99" t="s">
+      <c r="T48" s="97"/>
+      <c r="U48" s="97"/>
+      <c r="V48" s="97"/>
+      <c r="X48" s="97" t="s">
         <v>17</v>
       </c>
-      <c r="Y48" s="99"/>
-      <c r="Z48" s="99" t="s">
+      <c r="Y48" s="97"/>
+      <c r="Z48" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="AA48" s="99"/>
-      <c r="AB48" s="99" t="s">
+      <c r="AA48" s="97"/>
+      <c r="AB48" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="AC48" s="99"/>
-      <c r="AE48" s="104" t="s">
+      <c r="AC48" s="97"/>
+      <c r="AE48" s="102" t="s">
         <v>13</v>
       </c>
-      <c r="AF48" s="104"/>
-      <c r="AG48" s="104"/>
-      <c r="AH48" s="104"/>
-      <c r="AI48" s="104"/>
+      <c r="AF48" s="102"/>
+      <c r="AG48" s="102"/>
+      <c r="AH48" s="102"/>
+      <c r="AI48" s="102"/>
       <c r="AJ48" s="39"/>
       <c r="AO48" s="38" t="s">
         <v>165</v>
@@ -5124,13 +5008,8 @@
       </c>
       <c r="AR48" s="38"/>
       <c r="AS48" s="38"/>
-      <c r="AU48" s="62"/>
-      <c r="AV48" s="62"/>
-      <c r="AW48" s="62"/>
-      <c r="AX48" s="62"/>
-      <c r="AY48" s="62"/>
-    </row>
-    <row r="49" spans="1:51" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:45" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="26"/>
       <c r="C49" s="26"/>
       <c r="D49" s="6"/>
@@ -5148,21 +5027,21 @@
       <c r="P49" s="6"/>
       <c r="Q49" s="6"/>
       <c r="R49" s="6"/>
-      <c r="S49" s="104"/>
-      <c r="T49" s="104"/>
-      <c r="U49" s="104"/>
-      <c r="V49" s="104"/>
+      <c r="S49" s="102"/>
+      <c r="T49" s="102"/>
+      <c r="U49" s="102"/>
+      <c r="V49" s="102"/>
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
       <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="27"/>
-      <c r="AE49" s="104"/>
-      <c r="AF49" s="104"/>
-      <c r="AG49" s="104"/>
-      <c r="AH49" s="104"/>
-      <c r="AI49" s="104"/>
+      <c r="AE49" s="102"/>
+      <c r="AF49" s="102"/>
+      <c r="AG49" s="102"/>
+      <c r="AH49" s="102"/>
+      <c r="AI49" s="102"/>
       <c r="AJ49" s="39"/>
       <c r="AO49" s="38" t="s">
         <v>166</v>
@@ -5173,29 +5052,24 @@
       </c>
       <c r="AR49" s="38"/>
       <c r="AS49" s="38"/>
-      <c r="AU49" s="62"/>
-      <c r="AV49" s="62"/>
-      <c r="AW49" s="62"/>
-      <c r="AX49" s="62"/>
-      <c r="AY49" s="62"/>
-    </row>
-    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B50" s="120" t="s">
+      <c r="B50" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="120"/>
-      <c r="D50" s="120"/>
-      <c r="E50" s="120"/>
-      <c r="F50" s="120"/>
-      <c r="G50" s="120"/>
-      <c r="H50" s="120"/>
-      <c r="I50" s="120"/>
-      <c r="J50" s="120"/>
-      <c r="K50" s="120"/>
-      <c r="L50" s="120"/>
+      <c r="C50" s="118"/>
+      <c r="D50" s="118"/>
+      <c r="E50" s="118"/>
+      <c r="F50" s="118"/>
+      <c r="G50" s="118"/>
+      <c r="H50" s="118"/>
+      <c r="I50" s="118"/>
+      <c r="J50" s="118"/>
+      <c r="K50" s="118"/>
+      <c r="L50" s="118"/>
       <c r="Z50" s="3"/>
       <c r="AA50" s="3"/>
       <c r="AB50" s="3"/>
@@ -5213,13 +5087,8 @@
       </c>
       <c r="AR50" s="38"/>
       <c r="AS50" s="38"/>
-      <c r="AU50" s="62"/>
-      <c r="AV50" s="62"/>
-      <c r="AW50" s="62"/>
-      <c r="AX50" s="62"/>
-      <c r="AY50" s="62"/>
-    </row>
-    <row r="51" spans="1:51" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:45" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AJ51" s="39"/>
       <c r="AO51" s="38"/>
       <c r="AP51" s="38"/>
@@ -5228,17 +5097,12 @@
       </c>
       <c r="AR51" s="38"/>
       <c r="AS51" s="38"/>
-      <c r="AU51" s="62"/>
-      <c r="AV51" s="62"/>
-      <c r="AW51" s="62"/>
-      <c r="AX51" s="62"/>
-      <c r="AY51" s="62"/>
-    </row>
-    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A52" s="78" t="s">
+    </row>
+    <row r="52" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A52" s="76" t="s">
         <v>32</v>
       </c>
-      <c r="B52" s="78"/>
+      <c r="B52" s="76"/>
       <c r="C52" s="12" t="s">
         <v>33</v>
       </c>
@@ -5269,20 +5133,20 @@
       </c>
       <c r="S52" s="31"/>
       <c r="T52" s="33"/>
-      <c r="X52" s="78" t="s">
+      <c r="X52" s="76" t="s">
         <v>127</v>
       </c>
-      <c r="Y52" s="92"/>
-      <c r="Z52" s="105"/>
-      <c r="AA52" s="106"/>
-      <c r="AB52" s="106"/>
-      <c r="AC52" s="106"/>
-      <c r="AD52" s="106"/>
-      <c r="AE52" s="106"/>
-      <c r="AF52" s="106"/>
-      <c r="AG52" s="106"/>
-      <c r="AH52" s="106"/>
-      <c r="AI52" s="107"/>
+      <c r="Y52" s="90"/>
+      <c r="Z52" s="103"/>
+      <c r="AA52" s="104"/>
+      <c r="AB52" s="104"/>
+      <c r="AC52" s="104"/>
+      <c r="AD52" s="104"/>
+      <c r="AE52" s="104"/>
+      <c r="AF52" s="104"/>
+      <c r="AG52" s="104"/>
+      <c r="AH52" s="104"/>
+      <c r="AI52" s="105"/>
       <c r="AJ52" s="39"/>
       <c r="AO52" s="38"/>
       <c r="AP52" s="38"/>
@@ -5291,40 +5155,35 @@
       </c>
       <c r="AR52" s="38"/>
       <c r="AS52" s="38"/>
-      <c r="AU52" s="62"/>
-      <c r="AV52" s="62"/>
-      <c r="AW52" s="62"/>
-      <c r="AX52" s="62"/>
-      <c r="AY52" s="62"/>
-    </row>
-    <row r="53" spans="1:51" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:45" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G53" s="3"/>
-      <c r="H53" s="167" t="s">
+      <c r="H53" s="165" t="s">
         <v>37</v>
       </c>
-      <c r="I53" s="167"/>
-      <c r="J53" s="167"/>
-      <c r="L53" s="69" t="s">
+      <c r="I53" s="165"/>
+      <c r="J53" s="165"/>
+      <c r="L53" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="M53" s="69"/>
-      <c r="N53" s="69"/>
-      <c r="O53" s="69"/>
-      <c r="P53" s="69"/>
-      <c r="Q53" s="69"/>
-      <c r="R53" s="69"/>
-      <c r="S53" s="69"/>
-      <c r="T53" s="69"/>
-      <c r="Z53" s="108"/>
-      <c r="AA53" s="109"/>
-      <c r="AB53" s="109"/>
-      <c r="AC53" s="109"/>
-      <c r="AD53" s="109"/>
-      <c r="AE53" s="109"/>
-      <c r="AF53" s="109"/>
-      <c r="AG53" s="109"/>
-      <c r="AH53" s="109"/>
-      <c r="AI53" s="110"/>
+      <c r="M53" s="67"/>
+      <c r="N53" s="67"/>
+      <c r="O53" s="67"/>
+      <c r="P53" s="67"/>
+      <c r="Q53" s="67"/>
+      <c r="R53" s="67"/>
+      <c r="S53" s="67"/>
+      <c r="T53" s="67"/>
+      <c r="Z53" s="106"/>
+      <c r="AA53" s="107"/>
+      <c r="AB53" s="107"/>
+      <c r="AC53" s="107"/>
+      <c r="AD53" s="107"/>
+      <c r="AE53" s="107"/>
+      <c r="AF53" s="107"/>
+      <c r="AG53" s="107"/>
+      <c r="AH53" s="107"/>
+      <c r="AI53" s="108"/>
       <c r="AJ53" s="39"/>
       <c r="AO53" s="38"/>
       <c r="AP53" s="38"/>
@@ -5333,18 +5192,13 @@
       </c>
       <c r="AR53" s="38"/>
       <c r="AS53" s="38"/>
-      <c r="AU53" s="62"/>
-      <c r="AV53" s="62"/>
-      <c r="AW53" s="62"/>
-      <c r="AX53" s="62"/>
-      <c r="AY53" s="62"/>
-    </row>
-    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="C54" s="120" t="s">
+    </row>
+    <row r="54" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="C54" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="D54" s="120"/>
-      <c r="E54" s="120"/>
+      <c r="D54" s="118"/>
+      <c r="E54" s="118"/>
       <c r="F54" s="7">
         <v>8</v>
       </c>
@@ -5370,18 +5224,18 @@
       </c>
       <c r="S54" s="31"/>
       <c r="T54" s="33"/>
-      <c r="Z54" s="69" t="s">
+      <c r="Z54" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="AA54" s="69"/>
-      <c r="AB54" s="69"/>
-      <c r="AC54" s="69"/>
-      <c r="AD54" s="69"/>
-      <c r="AE54" s="69"/>
-      <c r="AF54" s="69"/>
-      <c r="AG54" s="69"/>
-      <c r="AH54" s="69"/>
-      <c r="AI54" s="69"/>
+      <c r="AA54" s="67"/>
+      <c r="AB54" s="67"/>
+      <c r="AC54" s="67"/>
+      <c r="AD54" s="67"/>
+      <c r="AE54" s="67"/>
+      <c r="AF54" s="67"/>
+      <c r="AG54" s="67"/>
+      <c r="AH54" s="67"/>
+      <c r="AI54" s="67"/>
       <c r="AJ54" s="39"/>
       <c r="AO54" s="38"/>
       <c r="AP54" s="38"/>
@@ -5390,417 +5244,218 @@
       </c>
       <c r="AR54" s="38"/>
       <c r="AS54" s="38"/>
-      <c r="AU54" s="62"/>
-      <c r="AV54" s="62"/>
-      <c r="AW54" s="62"/>
-      <c r="AX54" s="62"/>
-      <c r="AY54" s="62"/>
-    </row>
-    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:45" x14ac:dyDescent="0.25">
       <c r="G55" s="3"/>
-      <c r="H55" s="97" t="s">
+      <c r="H55" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="I55" s="97"/>
-      <c r="J55" s="97"/>
-      <c r="L55" s="69" t="s">
+      <c r="I55" s="95"/>
+      <c r="J55" s="95"/>
+      <c r="L55" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="M55" s="69"/>
-      <c r="N55" s="69"/>
-      <c r="O55" s="69"/>
-      <c r="P55" s="69"/>
-      <c r="Q55" s="69"/>
-      <c r="R55" s="69"/>
-      <c r="S55" s="69"/>
-      <c r="T55" s="69"/>
+      <c r="M55" s="67"/>
+      <c r="N55" s="67"/>
+      <c r="O55" s="67"/>
+      <c r="P55" s="67"/>
+      <c r="Q55" s="67"/>
+      <c r="R55" s="67"/>
+      <c r="S55" s="67"/>
+      <c r="T55" s="67"/>
       <c r="AJ55" s="39"/>
       <c r="AO55" s="38"/>
       <c r="AP55" s="38"/>
-      <c r="AQ55" s="38" t="s">
-        <v>179</v>
-      </c>
+      <c r="AQ55" s="38"/>
       <c r="AR55" s="38"/>
       <c r="AS55" s="38"/>
-      <c r="AU55" s="62"/>
-      <c r="AV55" s="62"/>
-      <c r="AW55" s="62"/>
-      <c r="AX55" s="62"/>
-      <c r="AY55" s="62"/>
-    </row>
-    <row r="56" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="95" t="s">
+    </row>
+    <row r="56" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="93" t="s">
         <v>57</v>
       </c>
-      <c r="B56" s="95"/>
-      <c r="C56" s="95"/>
-      <c r="D56" s="95"/>
-      <c r="E56" s="95"/>
-      <c r="F56" s="95"/>
-      <c r="G56" s="95"/>
-      <c r="H56" s="95"/>
-      <c r="I56" s="95"/>
-      <c r="J56" s="95"/>
-      <c r="K56" s="95"/>
-      <c r="L56" s="95"/>
-      <c r="M56" s="95"/>
-      <c r="N56" s="95"/>
-      <c r="O56" s="95"/>
-      <c r="P56" s="95"/>
-      <c r="Q56" s="95"/>
-      <c r="R56" s="95"/>
-      <c r="S56" s="95"/>
-      <c r="T56" s="95"/>
-      <c r="U56" s="95"/>
-      <c r="V56" s="95"/>
-      <c r="W56" s="95"/>
-      <c r="X56" s="95"/>
-      <c r="Y56" s="95"/>
-      <c r="Z56" s="95"/>
-      <c r="AA56" s="95"/>
-      <c r="AB56" s="95"/>
-      <c r="AC56" s="95"/>
-      <c r="AD56" s="95"/>
-      <c r="AE56" s="95"/>
-      <c r="AF56" s="95"/>
-      <c r="AG56" s="95"/>
-      <c r="AH56" s="95"/>
-      <c r="AI56" s="95"/>
+      <c r="B56" s="93"/>
+      <c r="C56" s="93"/>
+      <c r="D56" s="93"/>
+      <c r="E56" s="93"/>
+      <c r="F56" s="93"/>
+      <c r="G56" s="93"/>
+      <c r="H56" s="93"/>
+      <c r="I56" s="93"/>
+      <c r="J56" s="93"/>
+      <c r="K56" s="93"/>
+      <c r="L56" s="93"/>
+      <c r="M56" s="93"/>
+      <c r="N56" s="93"/>
+      <c r="O56" s="93"/>
+      <c r="P56" s="93"/>
+      <c r="Q56" s="93"/>
+      <c r="R56" s="93"/>
+      <c r="S56" s="93"/>
+      <c r="T56" s="93"/>
+      <c r="U56" s="93"/>
+      <c r="V56" s="93"/>
+      <c r="W56" s="93"/>
+      <c r="X56" s="93"/>
+      <c r="Y56" s="93"/>
+      <c r="Z56" s="93"/>
+      <c r="AA56" s="93"/>
+      <c r="AB56" s="93"/>
+      <c r="AC56" s="93"/>
+      <c r="AD56" s="93"/>
+      <c r="AE56" s="93"/>
+      <c r="AF56" s="93"/>
+      <c r="AG56" s="93"/>
+      <c r="AH56" s="93"/>
+      <c r="AI56" s="93"/>
       <c r="AJ56" s="39"/>
       <c r="AO56" s="38"/>
       <c r="AP56" s="38"/>
       <c r="AQ56" s="38"/>
       <c r="AR56" s="38"/>
       <c r="AS56" s="38"/>
-      <c r="AU56" s="62"/>
-      <c r="AV56" s="62"/>
-      <c r="AW56" s="62"/>
-      <c r="AX56" s="62"/>
-      <c r="AY56" s="62"/>
-    </row>
-    <row r="57" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="96"/>
-      <c r="B57" s="96"/>
-      <c r="C57" s="96"/>
-      <c r="D57" s="96"/>
-      <c r="E57" s="96"/>
-      <c r="F57" s="96"/>
-      <c r="G57" s="96"/>
-      <c r="H57" s="96"/>
-      <c r="I57" s="96"/>
-      <c r="J57" s="96"/>
-      <c r="K57" s="96"/>
-      <c r="L57" s="96"/>
-      <c r="M57" s="96"/>
-      <c r="N57" s="96"/>
-      <c r="O57" s="96"/>
-      <c r="P57" s="96"/>
-      <c r="Q57" s="96"/>
-      <c r="R57" s="96"/>
-      <c r="S57" s="96"/>
-      <c r="T57" s="96"/>
-      <c r="U57" s="96"/>
-      <c r="V57" s="96"/>
-      <c r="W57" s="96"/>
-      <c r="X57" s="96"/>
-      <c r="Y57" s="96"/>
-      <c r="Z57" s="96"/>
-      <c r="AA57" s="96"/>
-      <c r="AB57" s="96"/>
-      <c r="AC57" s="96"/>
-      <c r="AD57" s="96"/>
-      <c r="AE57" s="96"/>
-      <c r="AF57" s="96"/>
-      <c r="AG57" s="96"/>
-      <c r="AH57" s="96"/>
-      <c r="AI57" s="96"/>
+    </row>
+    <row r="57" spans="1:45" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="94"/>
+      <c r="B57" s="94"/>
+      <c r="C57" s="94"/>
+      <c r="D57" s="94"/>
+      <c r="E57" s="94"/>
+      <c r="F57" s="94"/>
+      <c r="G57" s="94"/>
+      <c r="H57" s="94"/>
+      <c r="I57" s="94"/>
+      <c r="J57" s="94"/>
+      <c r="K57" s="94"/>
+      <c r="L57" s="94"/>
+      <c r="M57" s="94"/>
+      <c r="N57" s="94"/>
+      <c r="O57" s="94"/>
+      <c r="P57" s="94"/>
+      <c r="Q57" s="94"/>
+      <c r="R57" s="94"/>
+      <c r="S57" s="94"/>
+      <c r="T57" s="94"/>
+      <c r="U57" s="94"/>
+      <c r="V57" s="94"/>
+      <c r="W57" s="94"/>
+      <c r="X57" s="94"/>
+      <c r="Y57" s="94"/>
+      <c r="Z57" s="94"/>
+      <c r="AA57" s="94"/>
+      <c r="AB57" s="94"/>
+      <c r="AC57" s="94"/>
+      <c r="AD57" s="94"/>
+      <c r="AE57" s="94"/>
+      <c r="AF57" s="94"/>
+      <c r="AG57" s="94"/>
+      <c r="AH57" s="94"/>
+      <c r="AI57" s="94"/>
       <c r="AJ57" s="39"/>
       <c r="AO57" s="38"/>
       <c r="AP57" s="38"/>
       <c r="AQ57" s="38"/>
       <c r="AR57" s="38"/>
       <c r="AS57" s="38"/>
-      <c r="AU57" s="62"/>
-      <c r="AV57" s="62"/>
-      <c r="AW57" s="62"/>
-      <c r="AX57" s="62"/>
-      <c r="AY57" s="62"/>
-    </row>
-    <row r="58" spans="1:51" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="93" t="s">
+    </row>
+    <row r="58" spans="1:45" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="B58" s="93"/>
-      <c r="C58" s="93"/>
-      <c r="D58" s="93"/>
-      <c r="E58" s="93"/>
-      <c r="F58" s="93"/>
-      <c r="G58" s="93"/>
-      <c r="H58" s="93"/>
-      <c r="I58" s="93"/>
-      <c r="J58" s="93"/>
-      <c r="K58" s="93"/>
-      <c r="L58" s="93"/>
-      <c r="M58" s="93"/>
-      <c r="N58" s="93"/>
-      <c r="O58" s="93"/>
-      <c r="P58" s="93"/>
-      <c r="Q58" s="93"/>
-      <c r="R58" s="93"/>
-      <c r="S58" s="93"/>
-      <c r="T58" s="93"/>
-      <c r="U58" s="93"/>
-      <c r="V58" s="93"/>
-      <c r="W58" s="93"/>
-      <c r="X58" s="93"/>
-      <c r="Y58" s="93"/>
-      <c r="Z58" s="93"/>
-      <c r="AA58" s="93"/>
-      <c r="AB58" s="93"/>
-      <c r="AC58" s="93"/>
-      <c r="AD58" s="93"/>
-      <c r="AE58" s="93"/>
-      <c r="AF58" s="93"/>
-      <c r="AG58" s="93"/>
-      <c r="AH58" s="93"/>
-      <c r="AI58" s="93"/>
+      <c r="B58" s="91"/>
+      <c r="C58" s="91"/>
+      <c r="D58" s="91"/>
+      <c r="E58" s="91"/>
+      <c r="F58" s="91"/>
+      <c r="G58" s="91"/>
+      <c r="H58" s="91"/>
+      <c r="I58" s="91"/>
+      <c r="J58" s="91"/>
+      <c r="K58" s="91"/>
+      <c r="L58" s="91"/>
+      <c r="M58" s="91"/>
+      <c r="N58" s="91"/>
+      <c r="O58" s="91"/>
+      <c r="P58" s="91"/>
+      <c r="Q58" s="91"/>
+      <c r="R58" s="91"/>
+      <c r="S58" s="91"/>
+      <c r="T58" s="91"/>
+      <c r="U58" s="91"/>
+      <c r="V58" s="91"/>
+      <c r="W58" s="91"/>
+      <c r="X58" s="91"/>
+      <c r="Y58" s="91"/>
+      <c r="Z58" s="91"/>
+      <c r="AA58" s="91"/>
+      <c r="AB58" s="91"/>
+      <c r="AC58" s="91"/>
+      <c r="AD58" s="91"/>
+      <c r="AE58" s="91"/>
+      <c r="AF58" s="91"/>
+      <c r="AG58" s="91"/>
+      <c r="AH58" s="91"/>
+      <c r="AI58" s="91"/>
       <c r="AJ58" s="39"/>
       <c r="AO58" s="38"/>
       <c r="AP58" s="38"/>
       <c r="AQ58" s="38"/>
       <c r="AR58" s="38"/>
       <c r="AS58" s="38"/>
-      <c r="AU58" s="62"/>
-      <c r="AV58" s="62"/>
-      <c r="AW58" s="62"/>
-      <c r="AX58" s="62"/>
-      <c r="AY58" s="62"/>
-    </row>
-    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A59" s="94"/>
-      <c r="B59" s="94"/>
-      <c r="C59" s="94"/>
-      <c r="D59" s="94"/>
-      <c r="E59" s="94"/>
-      <c r="F59" s="94"/>
-      <c r="G59" s="94"/>
-      <c r="H59" s="94"/>
-      <c r="I59" s="94"/>
-      <c r="J59" s="94"/>
-      <c r="K59" s="94"/>
-      <c r="L59" s="94"/>
-      <c r="M59" s="94"/>
-      <c r="N59" s="94"/>
-      <c r="O59" s="94"/>
-      <c r="P59" s="94"/>
-      <c r="Q59" s="94"/>
-      <c r="R59" s="94"/>
-      <c r="S59" s="94"/>
-      <c r="T59" s="94"/>
-      <c r="U59" s="94"/>
-      <c r="V59" s="94"/>
-      <c r="W59" s="94"/>
-      <c r="X59" s="94"/>
-      <c r="Y59" s="94"/>
-      <c r="Z59" s="94"/>
-      <c r="AA59" s="94"/>
-      <c r="AB59" s="94"/>
-      <c r="AC59" s="94"/>
-      <c r="AD59" s="94"/>
-      <c r="AE59" s="94"/>
-      <c r="AF59" s="94"/>
-      <c r="AG59" s="94"/>
-      <c r="AH59" s="94"/>
-      <c r="AI59" s="94"/>
+    </row>
+    <row r="59" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A59" s="92"/>
+      <c r="B59" s="92"/>
+      <c r="C59" s="92"/>
+      <c r="D59" s="92"/>
+      <c r="E59" s="92"/>
+      <c r="F59" s="92"/>
+      <c r="G59" s="92"/>
+      <c r="H59" s="92"/>
+      <c r="I59" s="92"/>
+      <c r="J59" s="92"/>
+      <c r="K59" s="92"/>
+      <c r="L59" s="92"/>
+      <c r="M59" s="92"/>
+      <c r="N59" s="92"/>
+      <c r="O59" s="92"/>
+      <c r="P59" s="92"/>
+      <c r="Q59" s="92"/>
+      <c r="R59" s="92"/>
+      <c r="S59" s="92"/>
+      <c r="T59" s="92"/>
+      <c r="U59" s="92"/>
+      <c r="V59" s="92"/>
+      <c r="W59" s="92"/>
+      <c r="X59" s="92"/>
+      <c r="Y59" s="92"/>
+      <c r="Z59" s="92"/>
+      <c r="AA59" s="92"/>
+      <c r="AB59" s="92"/>
+      <c r="AC59" s="92"/>
+      <c r="AD59" s="92"/>
+      <c r="AE59" s="92"/>
+      <c r="AF59" s="92"/>
+      <c r="AG59" s="92"/>
+      <c r="AH59" s="92"/>
+      <c r="AI59" s="92"/>
       <c r="AJ59" s="39"/>
       <c r="AO59" s="38"/>
       <c r="AP59" s="38"/>
       <c r="AQ59" s="38"/>
       <c r="AR59" s="38"/>
       <c r="AS59" s="38"/>
-      <c r="AU59" s="62"/>
-      <c r="AV59" s="62"/>
-      <c r="AW59" s="62"/>
-      <c r="AX59" s="62"/>
-      <c r="AY59" s="62"/>
-    </row>
-    <row r="60" spans="1:51" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:45" x14ac:dyDescent="0.25">
       <c r="AJ60" s="39"/>
       <c r="AO60" s="38"/>
       <c r="AP60" s="38"/>
       <c r="AQ60" s="38"/>
       <c r="AR60" s="38"/>
       <c r="AS60" s="38"/>
-      <c r="AU60" s="62"/>
-      <c r="AV60" s="62"/>
-      <c r="AW60" s="62"/>
-      <c r="AX60" s="62"/>
-      <c r="AY60" s="62"/>
-    </row>
-    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="AJ61" s="61"/>
-      <c r="AK61" s="61"/>
-      <c r="AL61" s="61"/>
-      <c r="AM61" s="61"/>
-      <c r="AN61" s="61"/>
-      <c r="AO61" s="61"/>
-      <c r="AP61" s="61"/>
-      <c r="AQ61" s="61"/>
-      <c r="AR61" s="61"/>
-      <c r="AS61" s="61"/>
-      <c r="AT61" s="62"/>
-      <c r="AU61" s="62"/>
-      <c r="AV61" s="62"/>
-      <c r="AW61" s="62"/>
-      <c r="AX61" s="62"/>
-      <c r="AY61" s="62"/>
-    </row>
-    <row r="62" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="AJ62" s="61"/>
-      <c r="AK62" s="61"/>
-      <c r="AL62" s="61"/>
-      <c r="AM62" s="61"/>
-      <c r="AN62" s="61"/>
-      <c r="AO62" s="61"/>
-      <c r="AP62" s="61"/>
-      <c r="AQ62" s="61"/>
-      <c r="AR62" s="61"/>
-      <c r="AS62" s="61"/>
-      <c r="AT62" s="62"/>
-      <c r="AU62" s="62"/>
-      <c r="AV62" s="62"/>
-      <c r="AW62" s="62"/>
-      <c r="AX62" s="62"/>
-      <c r="AY62" s="62"/>
-    </row>
-    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="AJ63" s="61"/>
-      <c r="AK63" s="61"/>
-      <c r="AL63" s="61"/>
-      <c r="AM63" s="61"/>
-      <c r="AN63" s="61"/>
-      <c r="AO63" s="61"/>
-      <c r="AP63" s="61"/>
-      <c r="AQ63" s="61"/>
-      <c r="AR63" s="61"/>
-      <c r="AS63" s="61"/>
-      <c r="AT63" s="62"/>
-      <c r="AU63" s="62"/>
-      <c r="AV63" s="62"/>
-      <c r="AW63" s="62"/>
-      <c r="AX63" s="62"/>
-      <c r="AY63" s="62"/>
-    </row>
-    <row r="64" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="AJ64" s="61"/>
-      <c r="AK64" s="61"/>
-      <c r="AL64" s="61"/>
-      <c r="AM64" s="61"/>
-      <c r="AN64" s="61"/>
-      <c r="AO64" s="61"/>
-      <c r="AP64" s="61"/>
-      <c r="AQ64" s="61"/>
-      <c r="AR64" s="61"/>
-      <c r="AS64" s="61"/>
-      <c r="AT64" s="62"/>
-      <c r="AU64" s="62"/>
-      <c r="AV64" s="62"/>
-      <c r="AW64" s="62"/>
-      <c r="AX64" s="62"/>
-      <c r="AY64" s="62"/>
-    </row>
-    <row r="65" spans="36:51" x14ac:dyDescent="0.25">
-      <c r="AJ65" s="61"/>
-      <c r="AK65" s="61"/>
-      <c r="AL65" s="61"/>
-      <c r="AM65" s="61"/>
-      <c r="AN65" s="61"/>
-      <c r="AO65" s="61"/>
-      <c r="AP65" s="61"/>
-      <c r="AQ65" s="61"/>
-      <c r="AR65" s="61"/>
-      <c r="AS65" s="61"/>
-      <c r="AT65" s="62"/>
-      <c r="AU65" s="62"/>
-      <c r="AV65" s="62"/>
-      <c r="AW65" s="62"/>
-      <c r="AX65" s="62"/>
-      <c r="AY65" s="62"/>
-    </row>
-    <row r="66" spans="36:51" x14ac:dyDescent="0.25">
-      <c r="AJ66" s="61"/>
-      <c r="AK66" s="61"/>
-      <c r="AL66" s="61"/>
-      <c r="AM66" s="61"/>
-      <c r="AN66" s="61"/>
-      <c r="AO66" s="61"/>
-      <c r="AP66" s="61"/>
-      <c r="AQ66" s="61"/>
-      <c r="AR66" s="61"/>
-      <c r="AS66" s="61"/>
-      <c r="AT66" s="62"/>
-      <c r="AU66" s="62"/>
-      <c r="AV66" s="62"/>
-      <c r="AW66" s="62"/>
-      <c r="AX66" s="62"/>
-      <c r="AY66" s="62"/>
-    </row>
-    <row r="67" spans="36:51" x14ac:dyDescent="0.25">
-      <c r="AJ67" s="61"/>
-      <c r="AK67" s="61"/>
-      <c r="AL67" s="61"/>
-      <c r="AM67" s="61"/>
-      <c r="AN67" s="61"/>
-      <c r="AO67" s="61"/>
-      <c r="AP67" s="61"/>
-      <c r="AQ67" s="61"/>
-      <c r="AR67" s="61"/>
-      <c r="AS67" s="61"/>
-      <c r="AT67" s="62"/>
-      <c r="AU67" s="62"/>
-      <c r="AV67" s="62"/>
-      <c r="AW67" s="62"/>
-      <c r="AX67" s="62"/>
-      <c r="AY67" s="62"/>
-    </row>
-    <row r="68" spans="36:51" x14ac:dyDescent="0.25">
-      <c r="AJ68" s="61"/>
-      <c r="AK68" s="61"/>
-      <c r="AL68" s="61"/>
-      <c r="AM68" s="61"/>
-      <c r="AN68" s="61"/>
-      <c r="AO68" s="61"/>
-      <c r="AP68" s="61"/>
-      <c r="AQ68" s="61"/>
-      <c r="AR68" s="61"/>
-      <c r="AS68" s="61"/>
-      <c r="AT68" s="62"/>
-      <c r="AU68" s="62"/>
-      <c r="AV68" s="62"/>
-      <c r="AW68" s="62"/>
-      <c r="AX68" s="62"/>
-      <c r="AY68" s="62"/>
-    </row>
-    <row r="69" spans="36:51" x14ac:dyDescent="0.25">
-      <c r="AJ69" s="61"/>
-      <c r="AK69" s="61"/>
-      <c r="AL69" s="61"/>
-      <c r="AM69" s="61"/>
-      <c r="AN69" s="61"/>
-      <c r="AO69" s="61"/>
-      <c r="AP69" s="61"/>
-      <c r="AQ69" s="61"/>
-      <c r="AR69" s="61"/>
-      <c r="AS69" s="61"/>
-      <c r="AT69" s="62"/>
-      <c r="AU69" s="62"/>
-      <c r="AV69" s="62"/>
-      <c r="AW69" s="62"/>
-      <c r="AX69" s="62"/>
-      <c r="AY69" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cioqgRC/vd2+AWqkR3ZTX8Q5EcifdSZbBjc0RApPK4QmYsmNHETIuh9Xd8Ed0Ehcpm87M4FIqJWc80mZSuVs9g==" saltValue="tEKD89B6LChaSpqwVbdykA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1aTPuEU3NhZjJxWnpGrRbE8z33Z8qF+21N+NTPhW09yNT+tGoBaneH6+Ah1jh0fdRbAFhL1OJNKW9GCixmfDGg==" saltValue="Glx0sIOwdUvuMibkfUajtw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <protectedRanges>
     <protectedRange sqref="A2 A5 A7:N7 A8:AI8 A9:I10 J10 A11:E12 F12 AI11 A13:H15 I15" name="Диапазон1"/>
     <protectedRange sqref="A2 A16:Q17 R17:U17 U16:AI17 Q19:AI19 AD18 W18 A18:P19 A20:AI20 C47 S48:V48 D49:R49 Y49:Z49 X48:AC48 AE48:AI49 E47:R47" name="Диапазон2"/>
@@ -6007,7 +5662,7 @@
     <mergeCell ref="S24:T24"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
-  <dataValidations count="11">
+  <dataValidations count="12">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R16:T16 R30:T31 O37:Q37 O40:Q40" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$AK$22:$AK$23</formula1>
     </dataValidation>
@@ -6023,8 +5678,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z18:AA18 E28:F28 E26:F26 E24:F24 E22:F22 Z47:AA47 W28:X28 W26:X26 W24:X24 W22:X22" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>$AP$19:$AP$30</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB47:AC47 AB18:AC18 G22:H22 G24:H24 G26:H26 G28:H28 Y22:Z22 Y24:Z24 Y26:Z26 Y28:Z28" xr:uid="{00000000-0002-0000-0000-000005000000}">
-      <formula1>$AQ$19:$AQ$55</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB18:AC18" xr:uid="{00000000-0002-0000-0000-000005000000}">
+      <formula1>$AQ$19:$AQ$54</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S47:V47" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>$AS$19:$AS$21</formula1>
@@ -6042,6 +5697,9 @@
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G22:H22 G24:H24 G26:H26 G28:H28 Y22:Z22 Y24:Z24 Y26:Z26 Y28:Z28 AB47:AC47" xr:uid="{776B72EB-27BC-481F-8B1D-D697A319E1B7}">
+      <formula1>$AQ$19:$AQ$54</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.43307086614173229" right="0.15748031496062992" top="0.15748031496062992" bottom="7.874015748031496E-2" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
